--- a/Holiday_Calendar_2026_2027.xlsx
+++ b/Holiday_Calendar_2026_2027.xlsx
@@ -22,7 +22,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Hong Kong'!$A$2:$H$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Singapore'!$A$2:$H$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'China'!$A$2:$H$76</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Squash Junior Events'!$A$2:$K$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Squash Junior Events'!$A$2:$L$53</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -19535,7 +19535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K64"/>
+  <dimension ref="A1:L64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" style="20" min="1" max="1"/>
@@ -19544,11 +19544,12 @@
     <col width="46" customWidth="1" style="20" min="4" max="4"/>
     <col width="20" customWidth="1" style="20" min="5" max="5"/>
     <col width="13" customWidth="1" style="20" min="6" max="6"/>
-    <col width="34" customWidth="1" style="20" min="7" max="7"/>
-    <col width="42" customWidth="1" style="20" min="8" max="8"/>
-    <col width="16" customWidth="1" style="20" min="9" max="9"/>
-    <col width="28" customWidth="1" style="20" min="10" max="10"/>
-    <col width="60" customWidth="1" style="20" min="11" max="11"/>
+    <col width="16" customWidth="1" style="20" min="7" max="7"/>
+    <col width="34" customWidth="1" style="20" min="8" max="8"/>
+    <col width="42" customWidth="1" style="20" min="9" max="9"/>
+    <col width="16" customWidth="1" style="20" min="10" max="10"/>
+    <col width="28" customWidth="1" style="20" min="11" max="11"/>
+    <col width="60" customWidth="1" style="20" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1" s="20">
@@ -19591,25 +19592,30 @@
       </c>
       <c r="G2" s="25" t="inlineStr">
         <is>
+          <t>Entry Deadline</t>
+        </is>
+      </c>
+      <c r="H2" s="25" t="inlineStr">
+        <is>
           <t>Organiser</t>
         </is>
       </c>
-      <c r="H2" s="25" t="inlineStr">
+      <c r="I2" s="25" t="inlineStr">
         <is>
           <t>Venue</t>
         </is>
       </c>
-      <c r="I2" s="25" t="inlineStr">
+      <c r="J2" s="25" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="J2" s="25" t="inlineStr">
+      <c r="K2" s="25" t="inlineStr">
         <is>
           <t>Age Groups</t>
         </is>
       </c>
-      <c r="K2" s="25" t="inlineStr">
+      <c r="L2" s="25" t="inlineStr">
         <is>
           <t>Notes / Source</t>
         </is>
@@ -19646,27 +19652,28 @@
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G3" s="27" t="inlineStr">
+      <c r="G3" s="26" t="inlineStr"/>
+      <c r="H3" s="27" t="inlineStr">
         <is>
           <t>England Squash / BJO</t>
         </is>
       </c>
-      <c r="H3" s="27" t="inlineStr">
+      <c r="I3" s="27" t="inlineStr">
         <is>
           <t>Birmingham, England</t>
         </is>
       </c>
-      <c r="I3" s="27" t="inlineStr">
+      <c r="J3" s="27" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="J3" s="27" t="inlineStr">
+      <c r="K3" s="27" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="K3" s="27" t="inlineStr">
+      <c r="L3" s="27" t="inlineStr">
         <is>
           <t>ESF Platinum | BJO 2027 = 2-6 Jan 2027. Source: britishjunioropen.com</t>
         </is>
@@ -19703,27 +19710,28 @@
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G4" s="29" t="inlineStr">
+      <c r="G4" s="28" t="inlineStr"/>
+      <c r="H4" s="29" t="inlineStr">
         <is>
           <t>Sri Lanka Squash / ASF</t>
         </is>
       </c>
-      <c r="H4" s="29" t="inlineStr">
+      <c r="I4" s="29" t="inlineStr">
         <is>
           <t>Colombo, Sri Lanka</t>
         </is>
       </c>
-      <c r="I4" s="29" t="inlineStr">
+      <c r="J4" s="29" t="inlineStr">
         <is>
           <t>Sri Lanka</t>
         </is>
       </c>
-      <c r="J4" s="29" t="inlineStr">
+      <c r="K4" s="29" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="K4" s="29" t="inlineStr">
+      <c r="L4" s="29" t="inlineStr">
         <is>
           <t>AJSS Silver. Source: asiansquash.org/eventpage/ajss-event</t>
         </is>
@@ -19760,27 +19768,28 @@
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G5" s="29" t="inlineStr">
+      <c r="G5" s="28" t="inlineStr"/>
+      <c r="H5" s="29" t="inlineStr">
         <is>
           <t>Korea Squash / ASF</t>
         </is>
       </c>
-      <c r="H5" s="29" t="inlineStr">
+      <c r="I5" s="29" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="I5" s="29" t="inlineStr">
+      <c r="J5" s="29" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="J5" s="29" t="inlineStr">
+      <c r="K5" s="29" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="K5" s="29" t="inlineStr">
+      <c r="L5" s="29" t="inlineStr">
         <is>
           <t>AJSS Silver. Source: asiansquash.org/eventpage/ajss-event</t>
         </is>
@@ -19817,27 +19826,28 @@
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G6" s="29" t="inlineStr">
+      <c r="G6" s="28" t="inlineStr"/>
+      <c r="H6" s="29" t="inlineStr">
         <is>
           <t>Singapore Squash / ASF</t>
         </is>
       </c>
-      <c r="H6" s="29" t="inlineStr">
+      <c r="I6" s="29" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="I6" s="29" t="inlineStr">
+      <c r="J6" s="29" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="J6" s="29" t="inlineStr">
+      <c r="K6" s="29" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="K6" s="29" t="inlineStr">
+      <c r="L6" s="29" t="inlineStr">
         <is>
           <t>AJSS Silver. Source: asiansquash.org/eventpage/ajss-event</t>
         </is>
@@ -19874,27 +19884,28 @@
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G7" s="31" t="inlineStr">
+      <c r="G7" s="30" t="inlineStr"/>
+      <c r="H7" s="31" t="inlineStr">
         <is>
           <t>ESF / German Squash Federation</t>
         </is>
       </c>
-      <c r="H7" s="31" t="inlineStr">
+      <c r="I7" s="31" t="inlineStr">
         <is>
           <t>Hamburg, Germany</t>
         </is>
       </c>
-      <c r="I7" s="31" t="inlineStr">
+      <c r="J7" s="31" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="J7" s="31" t="inlineStr">
+      <c r="K7" s="31" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="K7" s="31" t="inlineStr">
+      <c r="L7" s="31" t="inlineStr">
         <is>
           <t>ESF Junior Circuit Gold. Source: europeansquash.com</t>
         </is>
@@ -19931,27 +19942,28 @@
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G8" s="31" t="inlineStr">
+      <c r="G8" s="30" t="inlineStr"/>
+      <c r="H8" s="31" t="inlineStr">
         <is>
           <t>SRAFTKL / ASF</t>
         </is>
       </c>
-      <c r="H8" s="31" t="inlineStr">
+      <c r="I8" s="31" t="inlineStr">
         <is>
           <t>Kuala Lumpur, Malaysia</t>
         </is>
       </c>
-      <c r="I8" s="31" t="inlineStr">
+      <c r="J8" s="31" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="J8" s="31" t="inlineStr">
+      <c r="K8" s="31" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="K8" s="31" t="inlineStr">
+      <c r="L8" s="31" t="inlineStr">
         <is>
           <t>AJSS Gold. Source: asiansquash.org/eventpage/ajss-event</t>
         </is>
@@ -19988,27 +20000,28 @@
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G9" s="29" t="inlineStr">
+      <c r="G9" s="28" t="inlineStr"/>
+      <c r="H9" s="29" t="inlineStr">
         <is>
           <t>Negeri Sembilan Squash / ASF</t>
         </is>
       </c>
-      <c r="H9" s="29" t="inlineStr">
+      <c r="I9" s="29" t="inlineStr">
         <is>
           <t>Negeri Sembilan, Malaysia</t>
         </is>
       </c>
-      <c r="I9" s="29" t="inlineStr">
+      <c r="J9" s="29" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="J9" s="29" t="inlineStr">
+      <c r="K9" s="29" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="K9" s="29" t="inlineStr">
+      <c r="L9" s="29" t="inlineStr">
         <is>
           <t>AJSS Silver. Source: asiansquash.org/eventpage/ajss-event</t>
         </is>
@@ -20045,27 +20058,28 @@
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G10" s="29" t="inlineStr">
+      <c r="G10" s="28" t="inlineStr"/>
+      <c r="H10" s="29" t="inlineStr">
         <is>
           <t>Squash Australia / ASF</t>
         </is>
       </c>
-      <c r="H10" s="29" t="inlineStr">
+      <c r="I10" s="29" t="inlineStr">
         <is>
           <t>Melbourne Sports &amp; Aquatic Centre (MSAC), Melbourne</t>
         </is>
       </c>
-      <c r="I10" s="29" t="inlineStr">
+      <c r="J10" s="29" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="J10" s="29" t="inlineStr">
+      <c r="K10" s="29" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="K10" s="29" t="inlineStr">
+      <c r="L10" s="29" t="inlineStr">
         <is>
           <t>AJSS Silver (Zone A) trial inclusion. Also AJST Platinum &amp; WSF Registered. Source: asiansquash.org/eventpage/ajss-event + squashaus.com.au</t>
         </is>
@@ -20102,27 +20116,28 @@
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G11" s="31" t="inlineStr">
+      <c r="G11" s="30" t="inlineStr"/>
+      <c r="H11" s="31" t="inlineStr">
         <is>
           <t>India Squash / ASF</t>
         </is>
       </c>
-      <c r="H11" s="31" t="inlineStr">
+      <c r="I11" s="31" t="inlineStr">
         <is>
           <t>India (West)</t>
         </is>
       </c>
-      <c r="I11" s="31" t="inlineStr">
+      <c r="J11" s="31" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="J11" s="31" t="inlineStr">
+      <c r="K11" s="31" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="K11" s="31" t="inlineStr">
+      <c r="L11" s="31" t="inlineStr">
         <is>
           <t>AJSS Gold. Source: asiansquash.org/eventpage/ajss-event</t>
         </is>
@@ -20159,27 +20174,28 @@
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G12" s="43" t="inlineStr">
+      <c r="G12" s="42" t="inlineStr"/>
+      <c r="H12" s="43" t="inlineStr">
         <is>
           <t>Asian Squash Federation (ASF)</t>
         </is>
       </c>
-      <c r="H12" s="43" t="inlineStr">
+      <c r="I12" s="43" t="inlineStr">
         <is>
           <t>Zhangyi Garden / Panzhihua, China</t>
         </is>
       </c>
-      <c r="I12" s="43" t="inlineStr">
+      <c r="J12" s="43" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="J12" s="43" t="inlineStr">
+      <c r="K12" s="43" t="inlineStr">
         <is>
           <t>U13/U15/U17/U19 (B&amp;G — 8 categories)</t>
         </is>
       </c>
-      <c r="K12" s="43" t="inlineStr">
+      <c r="L12" s="43" t="inlineStr">
         <is>
           <t>8 gold medals. HKG &amp; PAK 2 each; CHN, SGP, MAS, IND 1 each. SGP's first Asian Junior title since 1987 (Kareena Sashikumar GU13). HKG Leung Ngo San (BU13) won from 2 games down. Source: thesquashsite.com/asian-junior-champs-2026-roundup</t>
         </is>
@@ -20216,27 +20232,28 @@
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G13" s="31" t="inlineStr">
+      <c r="G13" s="30" t="inlineStr"/>
+      <c r="H13" s="31" t="inlineStr">
         <is>
           <t>Singapore Squash / ASF</t>
         </is>
       </c>
-      <c r="H13" s="31" t="inlineStr">
+      <c r="I13" s="31" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="I13" s="31" t="inlineStr">
+      <c r="J13" s="31" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="J13" s="31" t="inlineStr">
+      <c r="K13" s="31" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="K13" s="31" t="inlineStr">
+      <c r="L13" s="31" t="inlineStr">
         <is>
           <t>AJSS Gold. Source: asiansquash.org/eventpage/ajss-event</t>
         </is>
@@ -20273,27 +20290,28 @@
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G14" s="29" t="inlineStr">
+      <c r="G14" s="28" t="inlineStr"/>
+      <c r="H14" s="29" t="inlineStr">
         <is>
           <t>India Squash / ASF</t>
         </is>
       </c>
-      <c r="H14" s="29" t="inlineStr">
+      <c r="I14" s="29" t="inlineStr">
         <is>
           <t>India (East)</t>
         </is>
       </c>
-      <c r="I14" s="29" t="inlineStr">
+      <c r="J14" s="29" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="J14" s="29" t="inlineStr">
+      <c r="K14" s="29" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="K14" s="29" t="inlineStr">
+      <c r="L14" s="29" t="inlineStr">
         <is>
           <t>AJSS Silver. Source: asiansquash.org/eventpage/ajss-event</t>
         </is>
@@ -20330,27 +20348,28 @@
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G15" s="31" t="inlineStr">
+      <c r="G15" s="30" t="inlineStr"/>
+      <c r="H15" s="31" t="inlineStr">
         <is>
           <t>Penang Squash / ASF</t>
         </is>
       </c>
-      <c r="H15" s="31" t="inlineStr">
+      <c r="I15" s="31" t="inlineStr">
         <is>
           <t>Penang, Malaysia</t>
         </is>
       </c>
-      <c r="I15" s="31" t="inlineStr">
+      <c r="J15" s="31" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="J15" s="31" t="inlineStr">
+      <c r="K15" s="31" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="K15" s="31" t="inlineStr">
+      <c r="L15" s="31" t="inlineStr">
         <is>
           <t>AJSS Gold. Source: asiansquash.org/eventpage/ajss-event</t>
         </is>
@@ -20387,27 +20406,28 @@
           <t>~ Estimated</t>
         </is>
       </c>
-      <c r="G16" s="45" t="inlineStr">
+      <c r="G16" s="44" t="inlineStr"/>
+      <c r="H16" s="45" t="inlineStr">
         <is>
           <t>ESF / Netherlands Squash</t>
         </is>
       </c>
-      <c r="H16" s="45" t="inlineStr">
+      <c r="I16" s="45" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="I16" s="45" t="inlineStr">
+      <c r="J16" s="45" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="J16" s="45" t="inlineStr">
+      <c r="K16" s="45" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="K16" s="45" t="inlineStr">
+      <c r="L16" s="45" t="inlineStr">
         <is>
           <t>ESF Junior Circuit Gold. Finals confirmed 5 Jul 2026; start date estimated. Source: europeansquash.com</t>
         </is>
@@ -20444,27 +20464,28 @@
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G17" s="27" t="inlineStr">
+      <c r="G17" s="26" t="inlineStr"/>
+      <c r="H17" s="27" t="inlineStr">
         <is>
           <t>European Squash Federation (ESF)</t>
         </is>
       </c>
-      <c r="H17" s="27" t="inlineStr">
+      <c r="I17" s="27" t="inlineStr">
         <is>
           <t>Sportwerk Hamburg, Germany</t>
         </is>
       </c>
-      <c r="I17" s="27" t="inlineStr">
+      <c r="J17" s="27" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="J17" s="27" t="inlineStr">
+      <c r="K17" s="27" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="K17" s="27" t="inlineStr">
+      <c r="L17" s="27" t="inlineStr">
         <is>
           <t>ESF Platinum. 215+ players. Second year at Hamburg. Source: europeansquash.com/event/european-junior-open-2026</t>
         </is>
@@ -20501,27 +20522,28 @@
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G18" s="29" t="inlineStr">
+      <c r="G18" s="28" t="inlineStr"/>
+      <c r="H18" s="29" t="inlineStr">
         <is>
           <t>China Squash / ASF</t>
         </is>
       </c>
-      <c r="H18" s="29" t="inlineStr">
+      <c r="I18" s="29" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="I18" s="29" t="inlineStr">
+      <c r="J18" s="29" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="J18" s="29" t="inlineStr">
+      <c r="K18" s="29" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="K18" s="29" t="inlineStr">
+      <c r="L18" s="29" t="inlineStr">
         <is>
           <t>AJSS Silver. Source: asiansquash.org/eventpage/ajss-event</t>
         </is>
@@ -20558,27 +20580,28 @@
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G19" s="47" t="inlineStr">
+      <c r="G19" s="46" t="inlineStr"/>
+      <c r="H19" s="47" t="inlineStr">
         <is>
           <t>World Squash Federation (WSF)</t>
         </is>
       </c>
-      <c r="H19" s="47" t="inlineStr">
+      <c r="I19" s="47" t="inlineStr">
         <is>
           <t>White Oaks Resort &amp; Spa, Niagara-on-the-Lake, Canada</t>
         </is>
       </c>
-      <c r="I19" s="47" t="inlineStr">
+      <c r="J19" s="47" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="J19" s="47" t="inlineStr">
+      <c r="K19" s="47" t="inlineStr">
         <is>
           <t>U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="K19" s="47" t="inlineStr">
+      <c r="L19" s="47" t="inlineStr">
         <is>
           <t>185 players, 24+ nations. Champions: Mohamad Zakaria (EGY — first 3-time Men's World Junior Champion), Anahat Singh (IND). First in Canada since 1984. Source: worldsquash.sport</t>
         </is>
@@ -20615,27 +20638,28 @@
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G20" s="47" t="inlineStr">
+      <c r="G20" s="46" t="inlineStr"/>
+      <c r="H20" s="47" t="inlineStr">
         <is>
           <t>World Squash Federation (WSF)</t>
         </is>
       </c>
-      <c r="H20" s="47" t="inlineStr">
+      <c r="I20" s="47" t="inlineStr">
         <is>
           <t>White Oaks Resort &amp; Spa, Niagara-on-the-Lake, Canada</t>
         </is>
       </c>
-      <c r="I20" s="47" t="inlineStr">
+      <c r="J20" s="47" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="J20" s="47" t="inlineStr">
+      <c r="K20" s="47" t="inlineStr">
         <is>
           <t>U19 (B&amp;G — team format)</t>
         </is>
       </c>
-      <c r="K20" s="47" t="inlineStr">
+      <c r="L20" s="47" t="inlineStr">
         <is>
           <t>Boys: 8 pools of 3. Girls: 4 pools of 4. Nigeria debuted in women's teams. Source: worldsquash.sport</t>
         </is>
@@ -20672,27 +20696,28 @@
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G21" s="27" t="inlineStr">
+      <c r="G21" s="26" t="inlineStr"/>
+      <c r="H21" s="27" t="inlineStr">
         <is>
           <t>Squash Association of Hong Kong, China (HKSA)</t>
         </is>
       </c>
-      <c r="H21" s="27" t="inlineStr">
+      <c r="I21" s="27" t="inlineStr">
         <is>
           <t>Cornwall St Squash Centre &amp; HK Squash Centre, Hong Kong</t>
         </is>
       </c>
-      <c r="I21" s="27" t="inlineStr">
+      <c r="J21" s="27" t="inlineStr">
         <is>
           <t>Hong Kong</t>
         </is>
       </c>
-      <c r="J21" s="27" t="inlineStr">
+      <c r="K21" s="27" t="inlineStr">
         <is>
           <t>U9/U11/U13/U15/U17/U19 (B&amp;G — 12 categories)</t>
         </is>
       </c>
-      <c r="K21" s="27" t="inlineStr">
+      <c r="L21" s="27" t="inlineStr">
         <is>
           <t>AJSS Platinum + WSF &amp; PSA Satellite Tour. Rounds/QF: 4-7 Aug (Cornwall St &amp; HKSC); SF/Final: 8-9 Aug (HKSC). PSA points: U17 &amp; U19. 850+ players from 16 countries. Sponsored by The Jessica Company; subvented by CSTB Arts &amp; Sport Dev Fund. Source: hksquash.org.hk + asiansquash.org</t>
         </is>
@@ -20729,27 +20754,28 @@
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G22" s="31" t="inlineStr">
+      <c r="G22" s="30" t="inlineStr"/>
+      <c r="H22" s="31" t="inlineStr">
         <is>
           <t>Korea Squash / ASF</t>
         </is>
       </c>
-      <c r="H22" s="31" t="inlineStr">
+      <c r="I22" s="31" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="I22" s="31" t="inlineStr">
+      <c r="J22" s="31" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="J22" s="31" t="inlineStr">
+      <c r="K22" s="31" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="K22" s="31" t="inlineStr">
+      <c r="L22" s="31" t="inlineStr">
         <is>
           <t>AJSS Gold. Source: asiansquash.org/eventpage/ajss-event</t>
         </is>
@@ -20786,27 +20812,28 @@
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G23" s="31" t="inlineStr">
+      <c r="G23" s="30" t="inlineStr"/>
+      <c r="H23" s="31" t="inlineStr">
         <is>
           <t>India Squash / ASF</t>
         </is>
       </c>
-      <c r="H23" s="31" t="inlineStr">
+      <c r="I23" s="31" t="inlineStr">
         <is>
           <t>Chennai, India</t>
         </is>
       </c>
-      <c r="I23" s="31" t="inlineStr">
+      <c r="J23" s="31" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="J23" s="31" t="inlineStr">
+      <c r="K23" s="31" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="K23" s="31" t="inlineStr">
+      <c r="L23" s="31" t="inlineStr">
         <is>
           <t>AJSS Gold. Entry deadline: 15 Jul 2026. Source: asiansquash.org/eventpage/ajss-event</t>
         </is>
@@ -20843,27 +20870,28 @@
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G24" s="29" t="inlineStr">
+      <c r="G24" s="28" t="inlineStr"/>
+      <c r="H24" s="29" t="inlineStr">
         <is>
           <t>Japan Squash / ASF</t>
         </is>
       </c>
-      <c r="H24" s="29" t="inlineStr">
+      <c r="I24" s="29" t="inlineStr">
         <is>
           <t>Yokohama &amp; Ebina, Japan</t>
         </is>
       </c>
-      <c r="I24" s="29" t="inlineStr">
+      <c r="J24" s="29" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="J24" s="29" t="inlineStr">
+      <c r="K24" s="29" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="K24" s="29" t="inlineStr">
+      <c r="L24" s="29" t="inlineStr">
         <is>
           <t>AJSS Silver. Entry deadline: 25 Jun 2026 12:00 JST. Source: asiansquash.org/eventpage/ajss-event</t>
         </is>
@@ -20900,27 +20928,28 @@
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G25" s="29" t="inlineStr">
+      <c r="G25" s="28" t="inlineStr"/>
+      <c r="H25" s="29" t="inlineStr">
         <is>
           <t>Qatar Squash / ASF</t>
         </is>
       </c>
-      <c r="H25" s="29" t="inlineStr">
+      <c r="I25" s="29" t="inlineStr">
         <is>
           <t>Doha, Qatar</t>
         </is>
       </c>
-      <c r="I25" s="29" t="inlineStr">
+      <c r="J25" s="29" t="inlineStr">
         <is>
           <t>Qatar</t>
         </is>
       </c>
-      <c r="J25" s="29" t="inlineStr">
+      <c r="K25" s="29" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="K25" s="29" t="inlineStr">
+      <c r="L25" s="29" t="inlineStr">
         <is>
           <t>AJSS Silver. Entry deadline: 6 Aug 2026. Source: asiansquash.org/eventpage/ajss-event</t>
         </is>
@@ -20957,27 +20986,28 @@
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G26" s="29" t="inlineStr">
+      <c r="G26" s="28" t="inlineStr"/>
+      <c r="H26" s="29" t="inlineStr">
         <is>
           <t>Chinese Taipei Squash / ASF</t>
         </is>
       </c>
-      <c r="H26" s="29" t="inlineStr">
+      <c r="I26" s="29" t="inlineStr">
         <is>
           <t>Taipei, Chinese Taipei</t>
         </is>
       </c>
-      <c r="I26" s="29" t="inlineStr">
+      <c r="J26" s="29" t="inlineStr">
         <is>
           <t>Chinese Taipei</t>
         </is>
       </c>
-      <c r="J26" s="29" t="inlineStr">
+      <c r="K26" s="29" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="K26" s="29" t="inlineStr">
+      <c r="L26" s="29" t="inlineStr">
         <is>
           <t>AJSS Silver — inaugural edition. Entry deadline: 5 Aug 2026. Source: asiansquash.org/eventpage/ajss-event</t>
         </is>
@@ -21014,27 +21044,28 @@
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G27" s="31" t="inlineStr">
+      <c r="G27" s="30" t="inlineStr"/>
+      <c r="H27" s="31" t="inlineStr">
         <is>
           <t>Macau Squash / ASF</t>
         </is>
       </c>
-      <c r="H27" s="31" t="inlineStr">
+      <c r="I27" s="31" t="inlineStr">
         <is>
           <t>Macau, China</t>
         </is>
       </c>
-      <c r="I27" s="31" t="inlineStr">
+      <c r="J27" s="31" t="inlineStr">
         <is>
           <t>Macau</t>
         </is>
       </c>
-      <c r="J27" s="31" t="inlineStr">
+      <c r="K27" s="31" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="K27" s="31" t="inlineStr">
+      <c r="L27" s="31" t="inlineStr">
         <is>
           <t>AJSS Gold. Entry deadline: 29 Jul 2026 12:00 Macau Time. Source: asiansquash.org/eventpage/ajss-event</t>
         </is>
@@ -21071,27 +21102,28 @@
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G28" s="27" t="inlineStr">
+      <c r="G28" s="26" t="inlineStr"/>
+      <c r="H28" s="27" t="inlineStr">
         <is>
           <t>Squash Rackets Federation of India / ASF</t>
         </is>
       </c>
-      <c r="H28" s="27" t="inlineStr">
+      <c r="I28" s="27" t="inlineStr">
         <is>
           <t>Kolkata, India</t>
         </is>
       </c>
-      <c r="I28" s="27" t="inlineStr">
+      <c r="J28" s="27" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="J28" s="27" t="inlineStr">
+      <c r="K28" s="27" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="K28" s="27" t="inlineStr">
+      <c r="L28" s="27" t="inlineStr">
         <is>
           <t>AJSS Platinum. Entry deadline: 12 Aug 2026. Source: asiansquash.org/eventpage/ajss-event</t>
         </is>
@@ -21128,27 +21160,28 @@
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G29" s="37" t="inlineStr">
+      <c r="G29" s="36" t="inlineStr"/>
+      <c r="H29" s="37" t="inlineStr">
         <is>
           <t>US Squash</t>
         </is>
       </c>
-      <c r="H29" s="37" t="inlineStr">
+      <c r="I29" s="37" t="inlineStr">
         <is>
           <t>Redwood Shores &amp; Redwood City, CA</t>
         </is>
       </c>
-      <c r="I29" s="37" t="inlineStr">
+      <c r="J29" s="37" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="J29" s="37" t="inlineStr">
+      <c r="K29" s="37" t="inlineStr">
         <is>
           <t>All junior age groups</t>
         </is>
       </c>
-      <c r="K29" s="37" t="inlineStr">
+      <c r="L29" s="37" t="inlineStr">
         <is>
           <t>US Squash Junior Championship Tour. Source: ussquash.org</t>
         </is>
@@ -21185,27 +21218,28 @@
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G30" s="49" t="inlineStr">
+      <c r="G30" s="48" t="inlineStr"/>
+      <c r="H30" s="49" t="inlineStr">
         <is>
           <t>Squash Rackets Association of Malaysia / ASF</t>
         </is>
       </c>
-      <c r="H30" s="49" t="inlineStr">
+      <c r="I30" s="49" t="inlineStr">
         <is>
           <t>Kuala Lumpur, Malaysia</t>
         </is>
       </c>
-      <c r="I30" s="49" t="inlineStr">
+      <c r="J30" s="49" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="J30" s="49" t="inlineStr">
+      <c r="K30" s="49" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="K30" s="49" t="inlineStr">
+      <c r="L30" s="49" t="inlineStr">
         <is>
           <t>AJSS Diamond — highest AJSS tier. Entry deadline: 14 Sep 2026 5pm Malaysian Time. Source: asiansquash.org/eventpage/ajss-event</t>
         </is>
@@ -21242,27 +21276,28 @@
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G31" s="29" t="inlineStr">
+      <c r="G31" s="28" t="inlineStr"/>
+      <c r="H31" s="29" t="inlineStr">
         <is>
           <t>Sri Lanka Squash / ASF</t>
         </is>
       </c>
-      <c r="H31" s="29" t="inlineStr">
+      <c r="I31" s="29" t="inlineStr">
         <is>
           <t>Ratmalana, Sri Lanka</t>
         </is>
       </c>
-      <c r="I31" s="29" t="inlineStr">
+      <c r="J31" s="29" t="inlineStr">
         <is>
           <t>Sri Lanka</t>
         </is>
       </c>
-      <c r="J31" s="29" t="inlineStr">
+      <c r="K31" s="29" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="K31" s="29" t="inlineStr">
+      <c r="L31" s="29" t="inlineStr">
         <is>
           <t>AJSS Silver. Entry deadline: 23 Sep 2026 23:59 Sri Lanka Time. Source: asiansquash.org/eventpage/ajss-event</t>
         </is>
@@ -21299,27 +21334,28 @@
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G32" s="37" t="inlineStr">
+      <c r="G32" s="36" t="inlineStr"/>
+      <c r="H32" s="37" t="inlineStr">
         <is>
           <t>US Squash</t>
         </is>
       </c>
-      <c r="H32" s="37" t="inlineStr">
+      <c r="I32" s="37" t="inlineStr">
         <is>
           <t>Washington, D.C.</t>
         </is>
       </c>
-      <c r="I32" s="37" t="inlineStr">
+      <c r="J32" s="37" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="J32" s="37" t="inlineStr">
+      <c r="K32" s="37" t="inlineStr">
         <is>
           <t>All junior age groups</t>
         </is>
       </c>
-      <c r="K32" s="37" t="inlineStr">
+      <c r="L32" s="37" t="inlineStr">
         <is>
           <t>US Squash Junior Championship Tour. Source: ussquash.org</t>
         </is>
@@ -21356,27 +21392,28 @@
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G33" s="27" t="inlineStr">
+      <c r="G33" s="26" t="inlineStr"/>
+      <c r="H33" s="27" t="inlineStr">
         <is>
           <t>KL Squash / ASF</t>
         </is>
       </c>
-      <c r="H33" s="27" t="inlineStr">
+      <c r="I33" s="27" t="inlineStr">
         <is>
           <t>Kuala Lumpur, Malaysia</t>
         </is>
       </c>
-      <c r="I33" s="27" t="inlineStr">
+      <c r="J33" s="27" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="J33" s="27" t="inlineStr">
+      <c r="K33" s="27" t="inlineStr">
         <is>
           <t>U9/U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="K33" s="27" t="inlineStr">
+      <c r="L33" s="27" t="inlineStr">
         <is>
           <t>AJSS Platinum. Entry deadline: 1 Oct 2026. Source: asiansquash.org/eventpage/ajss-event</t>
         </is>
@@ -21413,27 +21450,28 @@
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G34" s="27" t="inlineStr">
+      <c r="G34" s="26" t="inlineStr"/>
+      <c r="H34" s="27" t="inlineStr">
         <is>
           <t>Singapore Squash Rackets Association (SSRA) / ASF</t>
         </is>
       </c>
-      <c r="H34" s="27" t="inlineStr">
+      <c r="I34" s="27" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="I34" s="27" t="inlineStr">
+      <c r="J34" s="27" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="J34" s="27" t="inlineStr">
+      <c r="K34" s="27" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="K34" s="27" t="inlineStr">
+      <c r="L34" s="27" t="inlineStr">
         <is>
           <t>AJSS Platinum. Entry deadline: 1 Nov 2026. Source: asiansquash.org/eventpage/ajss-event</t>
         </is>
@@ -21470,27 +21508,28 @@
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G35" s="27" t="inlineStr">
+      <c r="G35" s="26" t="inlineStr"/>
+      <c r="H35" s="27" t="inlineStr">
         <is>
           <t>US Squash</t>
         </is>
       </c>
-      <c r="H35" s="27" t="inlineStr">
+      <c r="I35" s="27" t="inlineStr">
         <is>
           <t>Philadelphia, PA</t>
         </is>
       </c>
-      <c r="I35" s="27" t="inlineStr">
+      <c r="J35" s="27" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="J35" s="27" t="inlineStr">
+      <c r="K35" s="27" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="K35" s="27" t="inlineStr">
+      <c r="L35" s="27" t="inlineStr">
         <is>
           <t>One of the largest US junior squash events. Source: ussquash.org</t>
         </is>
@@ -21527,27 +21566,28 @@
           <t>~ Estimated</t>
         </is>
       </c>
-      <c r="G36" s="45" t="inlineStr">
+      <c r="G36" s="44" t="inlineStr"/>
+      <c r="H36" s="45" t="inlineStr">
         <is>
           <t>Squash Association of Hong Kong, China (HKSA)</t>
         </is>
       </c>
-      <c r="H36" s="45" t="inlineStr">
+      <c r="I36" s="45" t="inlineStr">
         <is>
           <t>Hong Kong Football Club &amp; HK Squash Centre, Hong Kong</t>
         </is>
       </c>
-      <c r="I36" s="45" t="inlineStr">
+      <c r="J36" s="45" t="inlineStr">
         <is>
           <t>Hong Kong</t>
         </is>
       </c>
-      <c r="J36" s="45" t="inlineStr">
+      <c r="K36" s="45" t="inlineStr">
         <is>
           <t>U9/U11/U13/U15/U17/U19 (B&amp;G — 12 categories)</t>
         </is>
       </c>
-      <c r="K36" s="45" t="inlineStr">
+      <c r="L36" s="45" t="inlineStr">
         <is>
           <t>AJSS Platinum. NOT YET listed on ASF page — dates estimated from prior years (2025 edition: 19-24 Dec 2025). Check hksquash.org.hk for official announcement.</t>
         </is>
@@ -21584,27 +21624,28 @@
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G37" s="27" t="inlineStr">
+      <c r="G37" s="26" t="inlineStr"/>
+      <c r="H37" s="27" t="inlineStr">
         <is>
           <t>England Squash / BJO</t>
         </is>
       </c>
-      <c r="H37" s="27" t="inlineStr">
+      <c r="I37" s="27" t="inlineStr">
         <is>
           <t>Birmingham, England</t>
         </is>
       </c>
-      <c r="I37" s="27" t="inlineStr">
+      <c r="J37" s="27" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="J37" s="27" t="inlineStr">
+      <c r="K37" s="27" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="K37" s="27" t="inlineStr">
+      <c r="L37" s="27" t="inlineStr">
         <is>
           <t>Officially confirmed 2-6 Jan 2027. 750+ players from 50+ countries. Source: britishjunioropen.com/save-the-dates-british-junior-open-2027</t>
         </is>
@@ -21641,27 +21682,28 @@
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G38" s="31" t="inlineStr">
+      <c r="G38" s="30" t="inlineStr"/>
+      <c r="H38" s="31" t="inlineStr">
         <is>
           <t>ESF / Czech Squash Federation</t>
         </is>
       </c>
-      <c r="H38" s="31" t="inlineStr">
+      <c r="I38" s="31" t="inlineStr">
         <is>
           <t>Prague, Czech Republic</t>
         </is>
       </c>
-      <c r="I38" s="31" t="inlineStr">
+      <c r="J38" s="31" t="inlineStr">
         <is>
           <t>Czech Republic</t>
         </is>
       </c>
-      <c r="J38" s="31" t="inlineStr">
+      <c r="K38" s="31" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="K38" s="31" t="inlineStr">
+      <c r="L38" s="31" t="inlineStr">
         <is>
           <t>ESF Junior Circuit Gold. Source: europeansquash.com</t>
         </is>
@@ -21698,27 +21740,28 @@
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G39" s="37" t="inlineStr">
+      <c r="G39" s="36" t="inlineStr"/>
+      <c r="H39" s="37" t="inlineStr">
         <is>
           <t>US Squash</t>
         </is>
       </c>
-      <c r="H39" s="37" t="inlineStr">
+      <c r="I39" s="37" t="inlineStr">
         <is>
           <t>Stamford / Norwalk, CT</t>
         </is>
       </c>
-      <c r="I39" s="37" t="inlineStr">
+      <c r="J39" s="37" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="J39" s="37" t="inlineStr">
+      <c r="K39" s="37" t="inlineStr">
         <is>
           <t>All junior age groups</t>
         </is>
       </c>
-      <c r="K39" s="37" t="inlineStr">
+      <c r="L39" s="37" t="inlineStr">
         <is>
           <t>US Squash Junior Championship Tour. Source: ussquash.org</t>
         </is>
@@ -21755,27 +21798,28 @@
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G40" s="39" t="inlineStr">
+      <c r="G40" s="38" t="inlineStr"/>
+      <c r="H40" s="39" t="inlineStr">
         <is>
           <t>ESF / Squash Slovenia</t>
         </is>
       </c>
-      <c r="H40" s="39" t="inlineStr">
+      <c r="I40" s="39" t="inlineStr">
         <is>
           <t>Ljubljana, Slovenia</t>
         </is>
       </c>
-      <c r="I40" s="39" t="inlineStr">
+      <c r="J40" s="39" t="inlineStr">
         <is>
           <t>Slovenia</t>
         </is>
       </c>
-      <c r="J40" s="39" t="inlineStr">
+      <c r="K40" s="39" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="K40" s="39" t="inlineStr">
+      <c r="L40" s="39" t="inlineStr">
         <is>
           <t>ESF Junior Circuit Bronze. Source: europeansquash.com</t>
         </is>
@@ -21812,27 +21856,28 @@
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G41" s="29" t="inlineStr">
+      <c r="G41" s="28" t="inlineStr"/>
+      <c r="H41" s="29" t="inlineStr">
         <is>
           <t>Sri Lanka Squash / ASF</t>
         </is>
       </c>
-      <c r="H41" s="29" t="inlineStr">
+      <c r="I41" s="29" t="inlineStr">
         <is>
           <t>Ratmalana, Sri Lanka</t>
         </is>
       </c>
-      <c r="I41" s="29" t="inlineStr">
+      <c r="J41" s="29" t="inlineStr">
         <is>
           <t>Sri Lanka</t>
         </is>
       </c>
-      <c r="J41" s="29" t="inlineStr">
+      <c r="K41" s="29" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="K41" s="29" t="inlineStr">
+      <c r="L41" s="29" t="inlineStr">
         <is>
           <t>AJSS Silver. Entry deadline: 4 Jan 2027. Source: asiansquash.org/eventpage/ajss-event</t>
         </is>
@@ -21869,27 +21914,28 @@
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G42" s="29" t="inlineStr">
+      <c r="G42" s="28" t="inlineStr"/>
+      <c r="H42" s="29" t="inlineStr">
         <is>
           <t>ESF / Swiss Squash</t>
         </is>
       </c>
-      <c r="H42" s="29" t="inlineStr">
+      <c r="I42" s="29" t="inlineStr">
         <is>
           <t>Langnau am Albis, Switzerland</t>
         </is>
       </c>
-      <c r="I42" s="29" t="inlineStr">
+      <c r="J42" s="29" t="inlineStr">
         <is>
           <t>Switzerland</t>
         </is>
       </c>
-      <c r="J42" s="29" t="inlineStr">
+      <c r="K42" s="29" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="K42" s="29" t="inlineStr">
+      <c r="L42" s="29" t="inlineStr">
         <is>
           <t>ESF Junior Circuit Silver. Source: europeansquash.com</t>
         </is>
@@ -21926,27 +21972,28 @@
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G43" s="37" t="inlineStr">
+      <c r="G43" s="36" t="inlineStr"/>
+      <c r="H43" s="37" t="inlineStr">
         <is>
           <t>US Squash</t>
         </is>
       </c>
-      <c r="H43" s="37" t="inlineStr">
+      <c r="I43" s="37" t="inlineStr">
         <is>
           <t>Houston, TX</t>
         </is>
       </c>
-      <c r="I43" s="37" t="inlineStr">
+      <c r="J43" s="37" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="J43" s="37" t="inlineStr">
+      <c r="K43" s="37" t="inlineStr">
         <is>
           <t>All junior age groups</t>
         </is>
       </c>
-      <c r="K43" s="37" t="inlineStr">
+      <c r="L43" s="37" t="inlineStr">
         <is>
           <t>US Squash Junior Championship Tour. Source: ussquash.org</t>
         </is>
@@ -21983,27 +22030,28 @@
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G44" s="31" t="inlineStr">
+      <c r="G44" s="30" t="inlineStr"/>
+      <c r="H44" s="31" t="inlineStr">
         <is>
           <t>ESF / German Squash Federation</t>
         </is>
       </c>
-      <c r="H44" s="31" t="inlineStr">
+      <c r="I44" s="31" t="inlineStr">
         <is>
           <t>Hamburg, Germany</t>
         </is>
       </c>
-      <c r="I44" s="31" t="inlineStr">
+      <c r="J44" s="31" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="J44" s="31" t="inlineStr">
+      <c r="K44" s="31" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="K44" s="31" t="inlineStr">
+      <c r="L44" s="31" t="inlineStr">
         <is>
           <t>ESF Junior Circuit Gold. Source: europeansquash.com</t>
         </is>
@@ -22040,27 +22088,28 @@
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G45" s="37" t="inlineStr">
+      <c r="G45" s="36" t="inlineStr"/>
+      <c r="H45" s="37" t="inlineStr">
         <is>
           <t>US Squash</t>
         </is>
       </c>
-      <c r="H45" s="37" t="inlineStr">
+      <c r="I45" s="37" t="inlineStr">
         <is>
           <t>Philadelphia, PA</t>
         </is>
       </c>
-      <c r="I45" s="37" t="inlineStr">
+      <c r="J45" s="37" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="J45" s="37" t="inlineStr">
+      <c r="K45" s="37" t="inlineStr">
         <is>
           <t>High School age groups</t>
         </is>
       </c>
-      <c r="K45" s="37" t="inlineStr">
+      <c r="L45" s="37" t="inlineStr">
         <is>
           <t>US national high school squash championships. Source: ussquash.org</t>
         </is>
@@ -22097,27 +22146,28 @@
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G46" s="43" t="inlineStr">
+      <c r="G46" s="42" t="inlineStr"/>
+      <c r="H46" s="43" t="inlineStr">
         <is>
           <t>Asian Squash Federation (ASF)</t>
         </is>
       </c>
-      <c r="H46" s="43" t="inlineStr">
+      <c r="I46" s="43" t="inlineStr">
         <is>
           <t>Thailand (venue TBC)</t>
         </is>
       </c>
-      <c r="I46" s="43" t="inlineStr">
+      <c r="J46" s="43" t="inlineStr">
         <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="J46" s="43" t="inlineStr">
+      <c r="K46" s="43" t="inlineStr">
         <is>
           <t>U19 (B&amp;G — team format)</t>
         </is>
       </c>
-      <c r="K46" s="43" t="inlineStr">
+      <c r="L46" s="43" t="inlineStr">
         <is>
           <t>Confirmed on ASF 2026-27 calendar. Exact venue TBC. Source: asiansquash.org + thesquashsite.com</t>
         </is>
@@ -22154,27 +22204,28 @@
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G47" s="29" t="inlineStr">
+      <c r="G47" s="28" t="inlineStr"/>
+      <c r="H47" s="29" t="inlineStr">
         <is>
           <t>ESF / Austrian Squash Federation</t>
         </is>
       </c>
-      <c r="H47" s="29" t="inlineStr">
+      <c r="I47" s="29" t="inlineStr">
         <is>
           <t>Vienna, Austria</t>
         </is>
       </c>
-      <c r="I47" s="29" t="inlineStr">
+      <c r="J47" s="29" t="inlineStr">
         <is>
           <t>Austria</t>
         </is>
       </c>
-      <c r="J47" s="29" t="inlineStr">
+      <c r="K47" s="29" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="K47" s="29" t="inlineStr">
+      <c r="L47" s="29" t="inlineStr">
         <is>
           <t>ESF Junior Circuit Silver. Source: europeansquash.com</t>
         </is>
@@ -22211,27 +22262,28 @@
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G48" s="37" t="inlineStr">
+      <c r="G48" s="36" t="inlineStr"/>
+      <c r="H48" s="37" t="inlineStr">
         <is>
           <t>US Squash</t>
         </is>
       </c>
-      <c r="H48" s="37" t="inlineStr">
+      <c r="I48" s="37" t="inlineStr">
         <is>
           <t>Philadelphia, PA</t>
         </is>
       </c>
-      <c r="I48" s="37" t="inlineStr">
+      <c r="J48" s="37" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="J48" s="37" t="inlineStr">
+      <c r="K48" s="37" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="K48" s="37" t="inlineStr">
+      <c r="L48" s="37" t="inlineStr">
         <is>
           <t>US national junior championships. Source: ussquash.org</t>
         </is>
@@ -22268,27 +22320,28 @@
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G49" s="39" t="inlineStr">
+      <c r="G49" s="38" t="inlineStr"/>
+      <c r="H49" s="39" t="inlineStr">
         <is>
           <t>ESF / Croatian Squash Federation</t>
         </is>
       </c>
-      <c r="H49" s="39" t="inlineStr">
+      <c r="I49" s="39" t="inlineStr">
         <is>
           <t>Zagreb, Croatia</t>
         </is>
       </c>
-      <c r="I49" s="39" t="inlineStr">
+      <c r="J49" s="39" t="inlineStr">
         <is>
           <t>Croatia</t>
         </is>
       </c>
-      <c r="J49" s="39" t="inlineStr">
+      <c r="K49" s="39" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="K49" s="39" t="inlineStr">
+      <c r="L49" s="39" t="inlineStr">
         <is>
           <t>ESF Junior Circuit Bronze. Source: europeansquash.com</t>
         </is>
@@ -22325,27 +22378,28 @@
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G50" s="37" t="inlineStr">
+      <c r="G50" s="36" t="inlineStr"/>
+      <c r="H50" s="37" t="inlineStr">
         <is>
           <t>US Squash</t>
         </is>
       </c>
-      <c r="H50" s="37" t="inlineStr">
+      <c r="I50" s="37" t="inlineStr">
         <is>
           <t>USA (venue TBC)</t>
         </is>
       </c>
-      <c r="I50" s="37" t="inlineStr">
+      <c r="J50" s="37" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="J50" s="37" t="inlineStr">
+      <c r="K50" s="37" t="inlineStr">
         <is>
           <t>All junior age groups</t>
         </is>
       </c>
-      <c r="K50" s="37" t="inlineStr">
+      <c r="L50" s="37" t="inlineStr">
         <is>
           <t>US Squash regional divisional event. Source: ussquash.org</t>
         </is>
@@ -22382,27 +22436,28 @@
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G51" s="39" t="inlineStr">
+      <c r="G51" s="38" t="inlineStr"/>
+      <c r="H51" s="39" t="inlineStr">
         <is>
           <t>ESF / Squash Norway</t>
         </is>
       </c>
-      <c r="H51" s="39" t="inlineStr">
+      <c r="I51" s="39" t="inlineStr">
         <is>
           <t>Lysaker, Norway</t>
         </is>
       </c>
-      <c r="I51" s="39" t="inlineStr">
+      <c r="J51" s="39" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="J51" s="39" t="inlineStr">
+      <c r="K51" s="39" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="K51" s="39" t="inlineStr">
+      <c r="L51" s="39" t="inlineStr">
         <is>
           <t>ESF Junior Circuit Bronze. Source: europeansquash.com</t>
         </is>
@@ -22439,27 +22494,28 @@
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G52" s="47" t="inlineStr">
+      <c r="G52" s="46" t="inlineStr"/>
+      <c r="H52" s="47" t="inlineStr">
         <is>
           <t>PSA World Tour / England Squash</t>
         </is>
       </c>
-      <c r="H52" s="47" t="inlineStr">
+      <c r="I52" s="47" t="inlineStr">
         <is>
           <t>London, England</t>
         </is>
       </c>
-      <c r="I52" s="47" t="inlineStr">
+      <c r="J52" s="47" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="J52" s="47" t="inlineStr">
+      <c r="K52" s="47" t="inlineStr">
         <is>
           <t>Open (professional)</t>
         </is>
       </c>
-      <c r="K52" s="47" t="inlineStr">
+      <c r="L52" s="47" t="inlineStr">
         <is>
           <t>Professional event — included for reference. Source: worldsquashchamps.com</t>
         </is>
@@ -22496,27 +22552,28 @@
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G53" s="47" t="inlineStr">
+      <c r="G53" s="46" t="inlineStr"/>
+      <c r="H53" s="47" t="inlineStr">
         <is>
           <t>World Squash Federation (WSF)</t>
         </is>
       </c>
-      <c r="H53" s="47" t="inlineStr">
+      <c r="I53" s="47" t="inlineStr">
         <is>
           <t>Karachi, Pakistan</t>
         </is>
       </c>
-      <c r="I53" s="47" t="inlineStr">
+      <c r="J53" s="47" t="inlineStr">
         <is>
           <t>Pakistan</t>
         </is>
       </c>
-      <c r="J53" s="47" t="inlineStr">
+      <c r="K53" s="47" t="inlineStr">
         <is>
           <t>U23 (B&amp;G)</t>
         </is>
       </c>
-      <c r="K53" s="47" t="inlineStr">
+      <c r="L53" s="47" t="inlineStr">
         <is>
           <t>WSF global event for under-23 players. Source: worldsquash.sport</t>
         </is>
@@ -22638,19 +22695,19 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:K53"/>
+  <autoFilter ref="A2:L53"/>
   <mergeCells count="11">
-    <mergeCell ref="B63:K63"/>
-    <mergeCell ref="B61:K61"/>
-    <mergeCell ref="B57:K57"/>
-    <mergeCell ref="A55:K55"/>
-    <mergeCell ref="B58:K58"/>
-    <mergeCell ref="B56:K56"/>
-    <mergeCell ref="B62:K62"/>
-    <mergeCell ref="B64:K64"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="B59:K59"/>
-    <mergeCell ref="B60:K60"/>
+    <mergeCell ref="B61:L61"/>
+    <mergeCell ref="B58:L58"/>
+    <mergeCell ref="B62:L62"/>
+    <mergeCell ref="B64:L64"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="B59:L59"/>
+    <mergeCell ref="B60:L60"/>
+    <mergeCell ref="B63:L63"/>
+    <mergeCell ref="A55:L55"/>
+    <mergeCell ref="B56:L56"/>
+    <mergeCell ref="B57:L57"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Holiday_Calendar_2026_2027.xlsx
+++ b/Holiday_Calendar_2026_2027.xlsx
@@ -13743,12 +13743,12 @@
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
-          <t>School Break - International</t>
+          <t>School Break - ISF Academy</t>
         </is>
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>ISF Academy</t>
         </is>
       </c>
       <c r="G19" s="9" t="inlineStr">
@@ -13895,12 +13895,12 @@
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>School Break - International</t>
+          <t>School Break - ISF Academy</t>
         </is>
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>ISF Academy</t>
         </is>
       </c>
       <c r="G23" s="9" t="inlineStr">
@@ -14017,12 +14017,12 @@
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>School Break - International</t>
+          <t>School Break - ISF Academy</t>
         </is>
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>ISF Academy</t>
         </is>
       </c>
       <c r="G26" s="9" t="inlineStr">
@@ -14165,12 +14165,12 @@
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>School Break - International</t>
+          <t>School Break - ISF Academy</t>
         </is>
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>ISF Academy</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
@@ -14393,12 +14393,12 @@
       </c>
       <c r="E36" s="10" t="inlineStr">
         <is>
-          <t>School Break - International</t>
+          <t>School Break - ISF Academy</t>
         </is>
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>ISF Academy</t>
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr">
@@ -14617,12 +14617,12 @@
       </c>
       <c r="E42" s="10" t="inlineStr">
         <is>
-          <t>School Break - International</t>
+          <t>School Break - ISF Academy</t>
         </is>
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>ISF Academy</t>
         </is>
       </c>
       <c r="G42" s="9" t="inlineStr">
@@ -14761,12 +14761,12 @@
       </c>
       <c r="E46" s="10" t="inlineStr">
         <is>
-          <t>School Break - International</t>
+          <t>School Break - ISF Academy</t>
         </is>
       </c>
       <c r="F46" s="10" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>ISF Academy</t>
         </is>
       </c>
       <c r="G46" s="9" t="inlineStr">
@@ -14837,12 +14837,12 @@
       </c>
       <c r="E48" s="10" t="inlineStr">
         <is>
-          <t>School Break - International</t>
+          <t>School Break - ISF Academy</t>
         </is>
       </c>
       <c r="F48" s="10" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>ISF Academy</t>
         </is>
       </c>
       <c r="G48" s="9" t="inlineStr">

--- a/Holiday_Calendar_2026_2027.xlsx
+++ b/Holiday_Calendar_2026_2027.xlsx
@@ -23,7 +23,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Hong Kong'!$A$2:$H$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Singapore'!$A$2:$H$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'China'!$A$2:$H$76</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Squash Junior Events'!$A$2:$L$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Squash Junior Events'!$A$2:$L$54</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -152,7 +152,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -199,6 +199,17 @@
       <right style="thin">
         <color rgb="00BFBFBF"/>
       </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="00BFBFBF"/>
       </top>
@@ -19698,7 +19709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L64"/>
+  <dimension ref="A1:L65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -21469,128 +21480,132 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
+          <t>31 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>15 Nov 2026</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>Hong Kong Junior Squash Championships 2026</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>National/Regional</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>25 Sep 2026</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>Squash Association of Hong Kong, China (HKSA)</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>Cornwall Street STTC &amp; Hong Kong Squash Centre, Hong Kong</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="K32" s="6" t="inlineStr">
+        <is>
+          <t>U9/U11/U13/U15/U17/U19 (B&amp;G)</t>
+        </is>
+      </c>
+      <c r="L32" s="6" t="inlineStr">
+        <is>
+          <t>HK Junior Ranking 3-star event. Played across 3 weekends: 31 Oct &amp; 1 Nov (CSPSC); 7-8 Nov (CSPSC); SF/Final 14-15 Nov (HKSC). Entry deadline: 25 Sep 2026. Source: hksquash.org.hk/public/tournaments/overview/id/391.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
           <t>13 Nov 2026</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>15 Nov 2026</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>Fri</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>US Mid-Atlantic JCT 2026</t>
         </is>
       </c>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="E33" s="6" t="inlineStr">
         <is>
           <t>National/Regional</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr"/>
+      <c r="H33" s="6" t="inlineStr">
         <is>
           <t>US Squash</t>
         </is>
       </c>
-      <c r="I32" s="6" t="inlineStr">
+      <c r="I33" s="6" t="inlineStr">
         <is>
           <t>Washington, D.C.</t>
         </is>
       </c>
-      <c r="J32" s="6" t="inlineStr">
+      <c r="J33" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="K32" s="6" t="inlineStr">
+      <c r="K33" s="6" t="inlineStr">
         <is>
           <t>All junior age groups</t>
         </is>
       </c>
-      <c r="L32" s="6" t="inlineStr">
+      <c r="L33" s="6" t="inlineStr">
         <is>
           <t>US Squash Junior Championship Tour. Source: ussquash.org</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="9" t="inlineStr">
-        <is>
-          <t>1 Dec 2026</t>
-        </is>
-      </c>
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t>6 Dec 2026</t>
-        </is>
-      </c>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="D33" s="10" t="inlineStr">
-        <is>
-          <t>REDtone 18th KL Junior Open Squash Championships 2026 ★</t>
-        </is>
-      </c>
-      <c r="E33" s="10" t="inlineStr">
-        <is>
-          <t>Platinum</t>
-        </is>
-      </c>
-      <c r="F33" s="9" t="inlineStr">
-        <is>
-          <t>✓ Confirmed</t>
-        </is>
-      </c>
-      <c r="G33" s="9" t="inlineStr"/>
-      <c r="H33" s="10" t="inlineStr">
-        <is>
-          <t>KL Squash / ASF</t>
-        </is>
-      </c>
-      <c r="I33" s="10" t="inlineStr">
-        <is>
-          <t>Kuala Lumpur, Malaysia</t>
-        </is>
-      </c>
-      <c r="J33" s="10" t="inlineStr">
-        <is>
-          <t>Malaysia</t>
-        </is>
-      </c>
-      <c r="K33" s="10" t="inlineStr">
-        <is>
-          <t>U9/U11/U13/U15/U17/U19 (B&amp;G)</t>
-        </is>
-      </c>
-      <c r="L33" s="10" t="inlineStr">
-        <is>
-          <t>AJSS Platinum. Entry deadline: 1 Oct 2026. Source: asiansquash.org/eventpage/ajss-event</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>8 Dec 2026</t>
+          <t>1 Dec 2026</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>13 Dec 2026</t>
+          <t>6 Dec 2026</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
@@ -21600,7 +21615,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>ONCOCARE Singapore Junior Open 2026 ★</t>
+          <t>REDtone 18th KL Junior Open Squash Championships 2026 ★</t>
         </is>
       </c>
       <c r="E34" s="10" t="inlineStr">
@@ -21616,49 +21631,49 @@
       <c r="G34" s="9" t="inlineStr"/>
       <c r="H34" s="10" t="inlineStr">
         <is>
-          <t>Singapore Squash Rackets Association (SSRA) / ASF</t>
+          <t>KL Squash / ASF</t>
         </is>
       </c>
       <c r="I34" s="10" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Kuala Lumpur, Malaysia</t>
         </is>
       </c>
       <c r="J34" s="10" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="K34" s="10" t="inlineStr">
         <is>
-          <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
+          <t>U9/U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
       <c r="L34" s="10" t="inlineStr">
         <is>
-          <t>AJSS Platinum. Entry deadline: 1 Nov 2026. Source: asiansquash.org/eventpage/ajss-event</t>
+          <t>AJSS Platinum. Entry deadline: 1 Oct 2026. Source: asiansquash.org/eventpage/ajss-event</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>19 Dec 2026</t>
+          <t>8 Dec 2026</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>23 Dec 2026</t>
+          <t>13 Dec 2026</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>US Junior Open 2026</t>
+          <t>ONCOCARE Singapore Junior Open 2026 ★</t>
         </is>
       </c>
       <c r="E35" s="10" t="inlineStr">
@@ -21674,382 +21689,382 @@
       <c r="G35" s="9" t="inlineStr"/>
       <c r="H35" s="10" t="inlineStr">
         <is>
+          <t>Singapore Squash Rackets Association (SSRA) / ASF</t>
+        </is>
+      </c>
+      <c r="I35" s="10" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="J35" s="10" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="K35" s="10" t="inlineStr">
+        <is>
+          <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
+        </is>
+      </c>
+      <c r="L35" s="10" t="inlineStr">
+        <is>
+          <t>AJSS Platinum. Entry deadline: 1 Nov 2026. Source: asiansquash.org/eventpage/ajss-event</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>19 Dec 2026</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>23 Dec 2026</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>US Junior Open 2026</t>
+        </is>
+      </c>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="F36" s="9" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="G36" s="9" t="inlineStr"/>
+      <c r="H36" s="10" t="inlineStr">
+        <is>
           <t>US Squash</t>
         </is>
       </c>
-      <c r="I35" s="10" t="inlineStr">
+      <c r="I36" s="10" t="inlineStr">
         <is>
           <t>Philadelphia, PA</t>
         </is>
       </c>
-      <c r="J35" s="10" t="inlineStr">
+      <c r="J36" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="K35" s="10" t="inlineStr">
+      <c r="K36" s="10" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L35" s="10" t="inlineStr">
+      <c r="L36" s="10" t="inlineStr">
         <is>
           <t>One of the largest US junior squash events. Source: ussquash.org</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="25" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="25" t="inlineStr">
         <is>
           <t>20 Dec 2026</t>
         </is>
       </c>
-      <c r="B36" s="25" t="inlineStr">
+      <c r="B37" s="25" t="inlineStr">
         <is>
           <t>26 Dec 2026</t>
         </is>
       </c>
-      <c r="C36" s="25" t="inlineStr">
+      <c r="C37" s="25" t="inlineStr">
         <is>
           <t>Sun</t>
         </is>
       </c>
-      <c r="D36" s="26" t="inlineStr">
+      <c r="D37" s="26" t="inlineStr">
         <is>
           <t>HKFC International Junior Squash Open 2026 (est.)</t>
         </is>
       </c>
-      <c r="E36" s="26" t="inlineStr">
+      <c r="E37" s="26" t="inlineStr">
         <is>
           <t>Platinum</t>
         </is>
       </c>
-      <c r="F36" s="25" t="inlineStr">
+      <c r="F37" s="25" t="inlineStr">
         <is>
           <t>~ Estimated</t>
         </is>
       </c>
-      <c r="G36" s="25" t="inlineStr"/>
-      <c r="H36" s="26" t="inlineStr">
+      <c r="G37" s="25" t="inlineStr"/>
+      <c r="H37" s="26" t="inlineStr">
         <is>
           <t>Squash Association of Hong Kong, China (HKSA)</t>
         </is>
       </c>
-      <c r="I36" s="26" t="inlineStr">
+      <c r="I37" s="26" t="inlineStr">
         <is>
           <t>Hong Kong Football Club &amp; HK Squash Centre, Hong Kong</t>
         </is>
       </c>
-      <c r="J36" s="26" t="inlineStr">
+      <c r="J37" s="26" t="inlineStr">
         <is>
           <t>Hong Kong</t>
         </is>
       </c>
-      <c r="K36" s="26" t="inlineStr">
+      <c r="K37" s="26" t="inlineStr">
         <is>
           <t>U9/U11/U13/U15/U17/U19 (B&amp;G — 12 categories)</t>
         </is>
       </c>
-      <c r="L36" s="26" t="inlineStr">
+      <c r="L37" s="26" t="inlineStr">
         <is>
           <t>AJSS Platinum. NOT YET listed on ASF page — dates estimated from prior years (2025 edition: 19-24 Dec 2025). Check hksquash.org.hk for official announcement.</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="9" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
         <is>
           <t>2 Jan 2027</t>
         </is>
       </c>
-      <c r="B37" s="9" t="inlineStr">
+      <c r="B38" s="9" t="inlineStr">
         <is>
           <t>6 Jan 2027</t>
         </is>
       </c>
-      <c r="C37" s="9" t="inlineStr">
+      <c r="C38" s="9" t="inlineStr">
         <is>
           <t>Sat</t>
         </is>
       </c>
-      <c r="D37" s="10" t="inlineStr">
+      <c r="D38" s="10" t="inlineStr">
         <is>
           <t>British Junior Open 2027</t>
         </is>
       </c>
-      <c r="E37" s="10" t="inlineStr">
+      <c r="E38" s="10" t="inlineStr">
         <is>
           <t>Platinum</t>
         </is>
       </c>
-      <c r="F37" s="9" t="inlineStr">
+      <c r="F38" s="9" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G37" s="9" t="inlineStr"/>
-      <c r="H37" s="10" t="inlineStr">
+      <c r="G38" s="9" t="inlineStr"/>
+      <c r="H38" s="10" t="inlineStr">
         <is>
           <t>England Squash / BJO</t>
         </is>
       </c>
-      <c r="I37" s="10" t="inlineStr">
+      <c r="I38" s="10" t="inlineStr">
         <is>
           <t>Birmingham, England</t>
         </is>
       </c>
-      <c r="J37" s="10" t="inlineStr">
+      <c r="J38" s="10" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="K37" s="10" t="inlineStr">
+      <c r="K38" s="10" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L37" s="10" t="inlineStr">
+      <c r="L38" s="10" t="inlineStr">
         <is>
           <t>Officially confirmed 2-6 Jan 2027. 750+ players from 50+ countries. Source: britishjunioropen.com/save-the-dates-british-junior-open-2027</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="7" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>14 Jan 2027</t>
         </is>
       </c>
-      <c r="B38" s="7" t="inlineStr">
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t>17 Jan 2027</t>
         </is>
       </c>
-      <c r="C38" s="7" t="inlineStr">
+      <c r="C39" s="7" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="D38" s="8" t="inlineStr">
+      <c r="D39" s="8" t="inlineStr">
         <is>
           <t>Czech Junior Open 2027</t>
         </is>
       </c>
-      <c r="E38" s="8" t="inlineStr">
+      <c r="E39" s="8" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="F38" s="7" t="inlineStr">
+      <c r="F39" s="7" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G38" s="7" t="inlineStr"/>
-      <c r="H38" s="8" t="inlineStr">
+      <c r="G39" s="7" t="inlineStr"/>
+      <c r="H39" s="8" t="inlineStr">
         <is>
           <t>ESF / Czech Squash Federation</t>
         </is>
       </c>
-      <c r="I38" s="8" t="inlineStr">
+      <c r="I39" s="8" t="inlineStr">
         <is>
           <t>Prague, Czech Republic</t>
         </is>
       </c>
-      <c r="J38" s="8" t="inlineStr">
+      <c r="J39" s="8" t="inlineStr">
         <is>
           <t>Czech Republic</t>
         </is>
       </c>
-      <c r="K38" s="8" t="inlineStr">
+      <c r="K39" s="8" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L38" s="8" t="inlineStr">
+      <c r="L39" s="8" t="inlineStr">
         <is>
           <t>ESF Junior Circuit Gold. Source: europeansquash.com</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>16 Jan 2027</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>18 Jan 2027</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>Sat</t>
         </is>
       </c>
-      <c r="D39" s="6" t="inlineStr">
+      <c r="D40" s="6" t="inlineStr">
         <is>
           <t>US Connecticut JCT 2027</t>
         </is>
       </c>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="E40" s="6" t="inlineStr">
         <is>
           <t>National/Regional</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr"/>
-      <c r="H39" s="6" t="inlineStr">
+      <c r="G40" s="5" t="inlineStr"/>
+      <c r="H40" s="6" t="inlineStr">
         <is>
           <t>US Squash</t>
         </is>
       </c>
-      <c r="I39" s="6" t="inlineStr">
+      <c r="I40" s="6" t="inlineStr">
         <is>
           <t>Stamford / Norwalk, CT</t>
         </is>
       </c>
-      <c r="J39" s="6" t="inlineStr">
+      <c r="J40" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="K39" s="6" t="inlineStr">
+      <c r="K40" s="6" t="inlineStr">
         <is>
           <t>All junior age groups</t>
         </is>
       </c>
-      <c r="L39" s="6" t="inlineStr">
+      <c r="L40" s="6" t="inlineStr">
         <is>
           <t>US Squash Junior Championship Tour. Source: ussquash.org</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>29 Jan 2027</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>31 Jan 2027</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>Fri</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="D41" s="4" t="inlineStr">
         <is>
           <t>Slovenia Junior Open 2027</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
+      <c r="E41" s="4" t="inlineStr">
         <is>
           <t>Bronze</t>
         </is>
       </c>
-      <c r="F40" s="3" t="inlineStr">
+      <c r="F41" s="3" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G40" s="3" t="inlineStr"/>
-      <c r="H40" s="4" t="inlineStr">
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="4" t="inlineStr">
         <is>
           <t>ESF / Squash Slovenia</t>
         </is>
       </c>
-      <c r="I40" s="4" t="inlineStr">
+      <c r="I41" s="4" t="inlineStr">
         <is>
           <t>Ljubljana, Slovenia</t>
         </is>
       </c>
-      <c r="J40" s="4" t="inlineStr">
+      <c r="J41" s="4" t="inlineStr">
         <is>
           <t>Slovenia</t>
         </is>
       </c>
-      <c r="K40" s="4" t="inlineStr">
+      <c r="K41" s="4" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L40" s="4" t="inlineStr">
+      <c r="L41" s="4" t="inlineStr">
         <is>
           <t>ESF Junior Circuit Bronze. Source: europeansquash.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="11" t="inlineStr">
-        <is>
-          <t>10 Feb 2027</t>
-        </is>
-      </c>
-      <c r="B41" s="11" t="inlineStr">
-        <is>
-          <t>14 Feb 2027</t>
-        </is>
-      </c>
-      <c r="C41" s="11" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="D41" s="12" t="inlineStr">
-        <is>
-          <t>Sri Lanka Junior Squash Open 2027 ★</t>
-        </is>
-      </c>
-      <c r="E41" s="12" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="F41" s="11" t="inlineStr">
-        <is>
-          <t>✓ Confirmed</t>
-        </is>
-      </c>
-      <c r="G41" s="11" t="inlineStr"/>
-      <c r="H41" s="12" t="inlineStr">
-        <is>
-          <t>Sri Lanka Squash / ASF</t>
-        </is>
-      </c>
-      <c r="I41" s="12" t="inlineStr">
-        <is>
-          <t>Ratmalana, Sri Lanka</t>
-        </is>
-      </c>
-      <c r="J41" s="12" t="inlineStr">
-        <is>
-          <t>Sri Lanka</t>
-        </is>
-      </c>
-      <c r="K41" s="12" t="inlineStr">
-        <is>
-          <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
-        </is>
-      </c>
-      <c r="L41" s="12" t="inlineStr">
-        <is>
-          <t>AJSS Silver. Entry deadline: 4 Jan 2027. Source: asiansquash.org/eventpage/ajss-event</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t>11 Feb 2027</t>
+          <t>10 Feb 2027</t>
         </is>
       </c>
       <c r="B42" s="11" t="inlineStr">
@@ -22059,12 +22074,12 @@
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>Swiss Junior Open 2027</t>
+          <t>Sri Lanka Junior Squash Open 2027 ★</t>
         </is>
       </c>
       <c r="E42" s="12" t="inlineStr">
@@ -22080,629 +22095,629 @@
       <c r="G42" s="11" t="inlineStr"/>
       <c r="H42" s="12" t="inlineStr">
         <is>
+          <t>Sri Lanka Squash / ASF</t>
+        </is>
+      </c>
+      <c r="I42" s="12" t="inlineStr">
+        <is>
+          <t>Ratmalana, Sri Lanka</t>
+        </is>
+      </c>
+      <c r="J42" s="12" t="inlineStr">
+        <is>
+          <t>Sri Lanka</t>
+        </is>
+      </c>
+      <c r="K42" s="12" t="inlineStr">
+        <is>
+          <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
+        </is>
+      </c>
+      <c r="L42" s="12" t="inlineStr">
+        <is>
+          <t>AJSS Silver. Entry deadline: 4 Jan 2027. Source: asiansquash.org/eventpage/ajss-event</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>11 Feb 2027</t>
+        </is>
+      </c>
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>14 Feb 2027</t>
+        </is>
+      </c>
+      <c r="C43" s="11" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="D43" s="12" t="inlineStr">
+        <is>
+          <t>Swiss Junior Open 2027</t>
+        </is>
+      </c>
+      <c r="E43" s="12" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="F43" s="11" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="G43" s="11" t="inlineStr"/>
+      <c r="H43" s="12" t="inlineStr">
+        <is>
           <t>ESF / Swiss Squash</t>
         </is>
       </c>
-      <c r="I42" s="12" t="inlineStr">
+      <c r="I43" s="12" t="inlineStr">
         <is>
           <t>Langnau am Albis, Switzerland</t>
         </is>
       </c>
-      <c r="J42" s="12" t="inlineStr">
+      <c r="J43" s="12" t="inlineStr">
         <is>
           <t>Switzerland</t>
         </is>
       </c>
-      <c r="K42" s="12" t="inlineStr">
+      <c r="K43" s="12" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L42" s="12" t="inlineStr">
+      <c r="L43" s="12" t="inlineStr">
         <is>
           <t>ESF Junior Circuit Silver. Source: europeansquash.com</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>13 Feb 2027</t>
         </is>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>15 Feb 2027</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
         <is>
           <t>Sat</t>
         </is>
       </c>
-      <c r="D43" s="6" t="inlineStr">
+      <c r="D44" s="6" t="inlineStr">
         <is>
           <t>US Texas JCT 2027</t>
         </is>
       </c>
-      <c r="E43" s="6" t="inlineStr">
+      <c r="E44" s="6" t="inlineStr">
         <is>
           <t>National/Regional</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="F44" s="5" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G43" s="5" t="inlineStr"/>
-      <c r="H43" s="6" t="inlineStr">
+      <c r="G44" s="5" t="inlineStr"/>
+      <c r="H44" s="6" t="inlineStr">
         <is>
           <t>US Squash</t>
         </is>
       </c>
-      <c r="I43" s="6" t="inlineStr">
+      <c r="I44" s="6" t="inlineStr">
         <is>
           <t>Houston, TX</t>
         </is>
       </c>
-      <c r="J43" s="6" t="inlineStr">
+      <c r="J44" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="K43" s="6" t="inlineStr">
+      <c r="K44" s="6" t="inlineStr">
         <is>
           <t>All junior age groups</t>
         </is>
       </c>
-      <c r="L43" s="6" t="inlineStr">
+      <c r="L44" s="6" t="inlineStr">
         <is>
           <t>US Squash Junior Championship Tour. Source: ussquash.org</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="7" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
         <is>
           <t>18 Feb 2027</t>
         </is>
       </c>
-      <c r="B44" s="7" t="inlineStr">
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t>21 Feb 2027</t>
         </is>
       </c>
-      <c r="C44" s="7" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="D44" s="8" t="inlineStr">
+      <c r="D45" s="8" t="inlineStr">
         <is>
           <t>German Junior Open 2027</t>
         </is>
       </c>
-      <c r="E44" s="8" t="inlineStr">
+      <c r="E45" s="8" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="F44" s="7" t="inlineStr">
+      <c r="F45" s="7" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G44" s="7" t="inlineStr"/>
-      <c r="H44" s="8" t="inlineStr">
+      <c r="G45" s="7" t="inlineStr"/>
+      <c r="H45" s="8" t="inlineStr">
         <is>
           <t>ESF / German Squash Federation</t>
         </is>
       </c>
-      <c r="I44" s="8" t="inlineStr">
+      <c r="I45" s="8" t="inlineStr">
         <is>
           <t>Hamburg, Germany</t>
         </is>
       </c>
-      <c r="J44" s="8" t="inlineStr">
+      <c r="J45" s="8" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="K44" s="8" t="inlineStr">
+      <c r="K45" s="8" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L44" s="8" t="inlineStr">
+      <c r="L45" s="8" t="inlineStr">
         <is>
           <t>ESF Junior Circuit Gold. Source: europeansquash.com</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>19 Feb 2027</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>21 Feb 2027</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
         <is>
           <t>Fri</t>
         </is>
       </c>
-      <c r="D45" s="6" t="inlineStr">
+      <c r="D46" s="6" t="inlineStr">
         <is>
           <t>US High School Championships 2027</t>
         </is>
       </c>
-      <c r="E45" s="6" t="inlineStr">
+      <c r="E46" s="6" t="inlineStr">
         <is>
           <t>National/Regional</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="F46" s="5" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G45" s="5" t="inlineStr"/>
-      <c r="H45" s="6" t="inlineStr">
+      <c r="G46" s="5" t="inlineStr"/>
+      <c r="H46" s="6" t="inlineStr">
         <is>
           <t>US Squash</t>
         </is>
       </c>
-      <c r="I45" s="6" t="inlineStr">
+      <c r="I46" s="6" t="inlineStr">
         <is>
           <t>Philadelphia, PA</t>
         </is>
       </c>
-      <c r="J45" s="6" t="inlineStr">
+      <c r="J46" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="K45" s="6" t="inlineStr">
+      <c r="K46" s="6" t="inlineStr">
         <is>
           <t>High School age groups</t>
         </is>
       </c>
-      <c r="L45" s="6" t="inlineStr">
+      <c r="L46" s="6" t="inlineStr">
         <is>
           <t>US national high school squash championships. Source: ussquash.org</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="23" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="23" t="inlineStr">
         <is>
           <t>23 Feb 2027</t>
         </is>
       </c>
-      <c r="B46" s="23" t="inlineStr">
+      <c r="B47" s="23" t="inlineStr">
         <is>
           <t>27 Feb 2027</t>
         </is>
       </c>
-      <c r="C46" s="23" t="inlineStr">
+      <c r="C47" s="23" t="inlineStr">
         <is>
           <t>Tue</t>
         </is>
       </c>
-      <c r="D46" s="24" t="inlineStr">
+      <c r="D47" s="24" t="inlineStr">
         <is>
           <t>23rd Asian Junior Team Championships 2027</t>
         </is>
       </c>
-      <c r="E46" s="24" t="inlineStr">
+      <c r="E47" s="24" t="inlineStr">
         <is>
           <t>Asian Championship</t>
         </is>
       </c>
-      <c r="F46" s="23" t="inlineStr">
+      <c r="F47" s="23" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G46" s="23" t="inlineStr"/>
-      <c r="H46" s="24" t="inlineStr">
+      <c r="G47" s="23" t="inlineStr"/>
+      <c r="H47" s="24" t="inlineStr">
         <is>
           <t>Asian Squash Federation (ASF)</t>
         </is>
       </c>
-      <c r="I46" s="24" t="inlineStr">
+      <c r="I47" s="24" t="inlineStr">
         <is>
           <t>Thailand (venue TBC)</t>
         </is>
       </c>
-      <c r="J46" s="24" t="inlineStr">
+      <c r="J47" s="24" t="inlineStr">
         <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="K46" s="24" t="inlineStr">
+      <c r="K47" s="24" t="inlineStr">
         <is>
           <t>U19 (B&amp;G — team format)</t>
         </is>
       </c>
-      <c r="L46" s="24" t="inlineStr">
+      <c r="L47" s="24" t="inlineStr">
         <is>
           <t>Confirmed on ASF 2026-27 calendar. Exact venue TBC. Source: asiansquash.org + thesquashsite.com</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="11" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="11" t="inlineStr">
         <is>
           <t>26 Feb 2027</t>
         </is>
       </c>
-      <c r="B47" s="11" t="inlineStr">
+      <c r="B48" s="11" t="inlineStr">
         <is>
           <t>28 Feb 2027</t>
         </is>
       </c>
-      <c r="C47" s="11" t="inlineStr">
+      <c r="C48" s="11" t="inlineStr">
         <is>
           <t>Fri</t>
         </is>
       </c>
-      <c r="D47" s="12" t="inlineStr">
+      <c r="D48" s="12" t="inlineStr">
         <is>
           <t>Austrian Junior Open 2027</t>
         </is>
       </c>
-      <c r="E47" s="12" t="inlineStr">
+      <c r="E48" s="12" t="inlineStr">
         <is>
           <t>Silver</t>
         </is>
       </c>
-      <c r="F47" s="11" t="inlineStr">
+      <c r="F48" s="11" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G47" s="11" t="inlineStr"/>
-      <c r="H47" s="12" t="inlineStr">
+      <c r="G48" s="11" t="inlineStr"/>
+      <c r="H48" s="12" t="inlineStr">
         <is>
           <t>ESF / Austrian Squash Federation</t>
         </is>
       </c>
-      <c r="I47" s="12" t="inlineStr">
+      <c r="I48" s="12" t="inlineStr">
         <is>
           <t>Vienna, Austria</t>
         </is>
       </c>
-      <c r="J47" s="12" t="inlineStr">
+      <c r="J48" s="12" t="inlineStr">
         <is>
           <t>Austria</t>
         </is>
       </c>
-      <c r="K47" s="12" t="inlineStr">
+      <c r="K48" s="12" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L47" s="12" t="inlineStr">
+      <c r="L48" s="12" t="inlineStr">
         <is>
           <t>ESF Junior Circuit Silver. Source: europeansquash.com</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>12 Mar 2027</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="B49" s="5" t="inlineStr">
         <is>
           <t>14 Mar 2027</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C49" s="5" t="inlineStr">
         <is>
           <t>Fri</t>
         </is>
       </c>
-      <c r="D48" s="6" t="inlineStr">
+      <c r="D49" s="6" t="inlineStr">
         <is>
           <t>US Junior Squash Championships 2027</t>
         </is>
       </c>
-      <c r="E48" s="6" t="inlineStr">
+      <c r="E49" s="6" t="inlineStr">
         <is>
           <t>National/Regional</t>
         </is>
       </c>
-      <c r="F48" s="5" t="inlineStr">
+      <c r="F49" s="5" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G48" s="5" t="inlineStr"/>
-      <c r="H48" s="6" t="inlineStr">
+      <c r="G49" s="5" t="inlineStr"/>
+      <c r="H49" s="6" t="inlineStr">
         <is>
           <t>US Squash</t>
         </is>
       </c>
-      <c r="I48" s="6" t="inlineStr">
+      <c r="I49" s="6" t="inlineStr">
         <is>
           <t>Philadelphia, PA</t>
         </is>
       </c>
-      <c r="J48" s="6" t="inlineStr">
+      <c r="J49" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="K48" s="6" t="inlineStr">
+      <c r="K49" s="6" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L48" s="6" t="inlineStr">
+      <c r="L49" s="6" t="inlineStr">
         <is>
           <t>US national junior championships. Source: ussquash.org</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>12 Mar 2027</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>14 Mar 2027</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>Fri</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr">
+      <c r="D50" s="4" t="inlineStr">
         <is>
           <t>Croatian Junior Open 2027</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
+      <c r="E50" s="4" t="inlineStr">
         <is>
           <t>Bronze</t>
         </is>
       </c>
-      <c r="F49" s="3" t="inlineStr">
+      <c r="F50" s="3" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G49" s="3" t="inlineStr"/>
-      <c r="H49" s="4" t="inlineStr">
+      <c r="G50" s="3" t="inlineStr"/>
+      <c r="H50" s="4" t="inlineStr">
         <is>
           <t>ESF / Croatian Squash Federation</t>
         </is>
       </c>
-      <c r="I49" s="4" t="inlineStr">
+      <c r="I50" s="4" t="inlineStr">
         <is>
           <t>Zagreb, Croatia</t>
         </is>
       </c>
-      <c r="J49" s="4" t="inlineStr">
+      <c r="J50" s="4" t="inlineStr">
         <is>
           <t>Croatia</t>
         </is>
       </c>
-      <c r="K49" s="4" t="inlineStr">
+      <c r="K50" s="4" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L49" s="4" t="inlineStr">
+      <c r="L50" s="4" t="inlineStr">
         <is>
           <t>ESF Junior Circuit Bronze. Source: europeansquash.com</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>19 Mar 2027</t>
         </is>
       </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="B51" s="5" t="inlineStr">
         <is>
           <t>21 Mar 2027</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C51" s="5" t="inlineStr">
         <is>
           <t>Fri</t>
         </is>
       </c>
-      <c r="D50" s="6" t="inlineStr">
+      <c r="D51" s="6" t="inlineStr">
         <is>
           <t>US Junior Divisional Championships 2027</t>
         </is>
       </c>
-      <c r="E50" s="6" t="inlineStr">
+      <c r="E51" s="6" t="inlineStr">
         <is>
           <t>National/Regional</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr">
+      <c r="F51" s="5" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G50" s="5" t="inlineStr"/>
-      <c r="H50" s="6" t="inlineStr">
+      <c r="G51" s="5" t="inlineStr"/>
+      <c r="H51" s="6" t="inlineStr">
         <is>
           <t>US Squash</t>
         </is>
       </c>
-      <c r="I50" s="6" t="inlineStr">
+      <c r="I51" s="6" t="inlineStr">
         <is>
           <t>USA (venue TBC)</t>
         </is>
       </c>
-      <c r="J50" s="6" t="inlineStr">
+      <c r="J51" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="K50" s="6" t="inlineStr">
+      <c r="K51" s="6" t="inlineStr">
         <is>
           <t>All junior age groups</t>
         </is>
       </c>
-      <c r="L50" s="6" t="inlineStr">
+      <c r="L51" s="6" t="inlineStr">
         <is>
           <t>US Squash regional divisional event. Source: ussquash.org</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
         <is>
           <t>19 Mar 2027</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>21 Mar 2027</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t>Fri</t>
         </is>
       </c>
-      <c r="D51" s="4" t="inlineStr">
+      <c r="D52" s="4" t="inlineStr">
         <is>
           <t>Norwegian Junior Open 2027</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
+      <c r="E52" s="4" t="inlineStr">
         <is>
           <t>Bronze</t>
         </is>
       </c>
-      <c r="F51" s="3" t="inlineStr">
+      <c r="F52" s="3" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G51" s="3" t="inlineStr"/>
-      <c r="H51" s="4" t="inlineStr">
+      <c r="G52" s="3" t="inlineStr"/>
+      <c r="H52" s="4" t="inlineStr">
         <is>
           <t>ESF / Squash Norway</t>
         </is>
       </c>
-      <c r="I51" s="4" t="inlineStr">
+      <c r="I52" s="4" t="inlineStr">
         <is>
           <t>Lysaker, Norway</t>
         </is>
       </c>
-      <c r="J51" s="4" t="inlineStr">
+      <c r="J52" s="4" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="K51" s="4" t="inlineStr">
+      <c r="K52" s="4" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L51" s="4" t="inlineStr">
+      <c r="L52" s="4" t="inlineStr">
         <is>
           <t>ESF Junior Circuit Bronze. Source: europeansquash.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="27" t="inlineStr">
-        <is>
-          <t>27 Mar 2027</t>
-        </is>
-      </c>
-      <c r="B52" s="27" t="inlineStr">
-        <is>
-          <t>4 Apr 2027</t>
-        </is>
-      </c>
-      <c r="C52" s="27" t="inlineStr">
-        <is>
-          <t>Sat</t>
-        </is>
-      </c>
-      <c r="D52" s="28" t="inlineStr">
-        <is>
-          <t>PSA World Championships 2026-27</t>
-        </is>
-      </c>
-      <c r="E52" s="28" t="inlineStr">
-        <is>
-          <t>World Championship</t>
-        </is>
-      </c>
-      <c r="F52" s="27" t="inlineStr">
-        <is>
-          <t>✓ Confirmed</t>
-        </is>
-      </c>
-      <c r="G52" s="27" t="inlineStr"/>
-      <c r="H52" s="28" t="inlineStr">
-        <is>
-          <t>PSA World Tour / England Squash</t>
-        </is>
-      </c>
-      <c r="I52" s="28" t="inlineStr">
-        <is>
-          <t>London, England</t>
-        </is>
-      </c>
-      <c r="J52" s="28" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="K52" s="28" t="inlineStr">
-        <is>
-          <t>Open (professional)</t>
-        </is>
-      </c>
-      <c r="L52" s="28" t="inlineStr">
-        <is>
-          <t>Professional event — included for reference. Source: worldsquashchamps.com</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="27" t="inlineStr">
         <is>
-          <t>7 Jun 2027</t>
+          <t>27 Mar 2027</t>
         </is>
       </c>
       <c r="B53" s="27" t="inlineStr">
         <is>
-          <t>13 Jun 2027</t>
+          <t>4 Apr 2027</t>
         </is>
       </c>
       <c r="C53" s="27" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="D53" s="28" t="inlineStr">
         <is>
-          <t>WSF World Under-23 Championships 2027</t>
+          <t>PSA World Championships 2026-27</t>
         </is>
       </c>
       <c r="E53" s="28" t="inlineStr">
@@ -22718,158 +22733,216 @@
       <c r="G53" s="27" t="inlineStr"/>
       <c r="H53" s="28" t="inlineStr">
         <is>
+          <t>PSA World Tour / England Squash</t>
+        </is>
+      </c>
+      <c r="I53" s="28" t="inlineStr">
+        <is>
+          <t>London, England</t>
+        </is>
+      </c>
+      <c r="J53" s="28" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="K53" s="28" t="inlineStr">
+        <is>
+          <t>Open (professional)</t>
+        </is>
+      </c>
+      <c r="L53" s="28" t="inlineStr">
+        <is>
+          <t>Professional event — included for reference. Source: worldsquashchamps.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="27" t="inlineStr">
+        <is>
+          <t>7 Jun 2027</t>
+        </is>
+      </c>
+      <c r="B54" s="27" t="inlineStr">
+        <is>
+          <t>13 Jun 2027</t>
+        </is>
+      </c>
+      <c r="C54" s="27" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="D54" s="28" t="inlineStr">
+        <is>
+          <t>WSF World Under-23 Championships 2027</t>
+        </is>
+      </c>
+      <c r="E54" s="28" t="inlineStr">
+        <is>
+          <t>World Championship</t>
+        </is>
+      </c>
+      <c r="F54" s="27" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="G54" s="27" t="inlineStr"/>
+      <c r="H54" s="28" t="inlineStr">
+        <is>
           <t>World Squash Federation (WSF)</t>
         </is>
       </c>
-      <c r="I53" s="28" t="inlineStr">
+      <c r="I54" s="28" t="inlineStr">
         <is>
           <t>Karachi, Pakistan</t>
         </is>
       </c>
-      <c r="J53" s="28" t="inlineStr">
+      <c r="J54" s="28" t="inlineStr">
         <is>
           <t>Pakistan</t>
         </is>
       </c>
-      <c r="K53" s="28" t="inlineStr">
+      <c r="K54" s="28" t="inlineStr">
         <is>
           <t>U23 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L53" s="28" t="inlineStr">
+      <c r="L54" s="28" t="inlineStr">
         <is>
           <t>WSF global event for under-23 players. Source: worldsquash.sport</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="31" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="31" t="inlineStr">
         <is>
           <t>COLOUR KEY — AJSS Levels: Diamond &gt; Platinum &gt; Gold &gt; Silver &gt; Bronze</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="28" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="28" t="inlineStr">
         <is>
           <t>World Championship</t>
         </is>
       </c>
-      <c r="B56" s="28" t="inlineStr">
+      <c r="B57" s="28" t="inlineStr">
         <is>
           <t>WSF / PSA global championship — pinnacle events</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="24" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="24" t="inlineStr">
         <is>
           <t>Asian Championship</t>
         </is>
       </c>
-      <c r="B57" s="24" t="inlineStr">
+      <c r="B58" s="24" t="inlineStr">
         <is>
           <t>ASF continental championships (Asian Junior Individual &amp; Team)</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="30" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="30" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="B58" s="30" t="inlineStr">
+      <c r="B59" s="30" t="inlineStr">
         <is>
           <t>AJSS Diamond — highest AJSS tier (e.g. Milo Malaysia)</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="10" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="10" t="inlineStr">
         <is>
           <t>Platinum</t>
         </is>
       </c>
-      <c r="B59" s="10" t="inlineStr">
+      <c r="B60" s="10" t="inlineStr">
         <is>
           <t>AJSS Platinum / ESF Platinum — highest open tier (HK Junior, BJO, Singapore JO, KL JO, Indian JO)</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="8" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="8" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="B60" s="8" t="inlineStr">
+      <c r="B61" s="8" t="inlineStr">
         <is>
           <t>AJSS Gold / ESF Gold — second tier (Korea, Japan, Penang, Lion City, Slams, Dutch JO, German JO)</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="12" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="12" t="inlineStr">
         <is>
           <t>Silver</t>
         </is>
       </c>
-      <c r="B61" s="12" t="inlineStr">
+      <c r="B62" s="12" t="inlineStr">
         <is>
           <t>AJSS Silver / ESF Silver — third tier (Sri Lanka, Australia, China, Qatar, Chinese Taipei, Swiss JO)</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="4" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
         <is>
           <t>Bronze</t>
         </is>
       </c>
-      <c r="B62" s="4" t="inlineStr">
+      <c r="B63" s="4" t="inlineStr">
         <is>
           <t>ESF Bronze — fourth tier European circuit (Slovenia, Croatia, Norway)</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="6" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
         <is>
           <t>National/Regional</t>
         </is>
       </c>
-      <c r="B63" s="6" t="inlineStr">
+      <c r="B64" s="6" t="inlineStr">
         <is>
           <t>National tour stops and domestic championships (US Squash JCT / High School / Divisional)</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="26" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="26" t="inlineStr">
         <is>
           <t>~ Estimated</t>
         </is>
       </c>
-      <c r="B64" s="26" t="inlineStr">
+      <c r="B65" s="26" t="inlineStr">
         <is>
           <t>AMBER = dates not yet officially confirmed — verify with the relevant federation before travel/planning</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:L53"/>
+  <autoFilter ref="A2:L54"/>
   <mergeCells count="11">
-    <mergeCell ref="B61:L61"/>
+    <mergeCell ref="B65:L65"/>
     <mergeCell ref="B58:L58"/>
     <mergeCell ref="B62:L62"/>
     <mergeCell ref="B64:L64"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="B59:L59"/>
+    <mergeCell ref="A56:L56"/>
     <mergeCell ref="B60:L60"/>
     <mergeCell ref="B63:L63"/>
-    <mergeCell ref="A55:L55"/>
-    <mergeCell ref="B56:L56"/>
+    <mergeCell ref="B61:L61"/>
     <mergeCell ref="B57:L57"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Holiday_Calendar_2026_2027.xlsx
+++ b/Holiday_Calendar_2026_2027.xlsx
@@ -23,7 +23,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Hong Kong'!$A$2:$H$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Singapore'!$A$2:$H$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'China'!$A$2:$H$76</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Squash Junior Events'!$A$2:$L$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Squash Junior Events'!$A$2:$L$62</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19709,7 +19709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L65"/>
+  <dimension ref="A1:L73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -20436,22 +20436,22 @@
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>22 Jun 2026</t>
+          <t>10 Jun 2026</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>27 Jun 2026</t>
+          <t>14 Jun 2026</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>Eastern Slam 2026 ★</t>
+          <t>4th Southeast Asian Junior Individual Championships 2026</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
@@ -20467,977 +20467,977 @@
       <c r="G14" s="11" t="inlineStr"/>
       <c r="H14" s="12" t="inlineStr">
         <is>
+          <t>Squash Philippines / ASF</t>
+        </is>
+      </c>
+      <c r="I14" s="12" t="inlineStr">
+        <is>
+          <t>Manila, Philippines</t>
+        </is>
+      </c>
+      <c r="J14" s="12" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="K14" s="12" t="inlineStr">
+        <is>
+          <t>U19 (B&amp;G)</t>
+        </is>
+      </c>
+      <c r="L14" s="12" t="inlineStr">
+        <is>
+          <t>AJSS Silver. SEA Junior Individual Champs. Source: ASF handbook / asiansquash.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>11 Jun 2026</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>14 Jun 2026</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>Italian Junior Open 2026</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="inlineStr"/>
+      <c r="H15" s="12" t="inlineStr">
+        <is>
+          <t>ESF / Italian Squash Federation</t>
+        </is>
+      </c>
+      <c r="I15" s="12" t="inlineStr">
+        <is>
+          <t>Riccione (RN), Italy</t>
+        </is>
+      </c>
+      <c r="J15" s="12" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="K15" s="12" t="inlineStr">
+        <is>
+          <t>U13/U15/U17/U19 (B&amp;G)</t>
+        </is>
+      </c>
+      <c r="L15" s="12" t="inlineStr">
+        <is>
+          <t>ESF Junior Circuit Silver. Source: europeansquash.com/event/italian-junior-open-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>19 Jun 2026</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>21 Jun 2026</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>Portuguese Junior Open 2026</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="F16" s="11" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="G16" s="11" t="inlineStr"/>
+      <c r="H16" s="12" t="inlineStr">
+        <is>
+          <t>ESF / Portuguese Squash Federation</t>
+        </is>
+      </c>
+      <c r="I16" s="12" t="inlineStr">
+        <is>
+          <t>Proracket Squash &amp; Padel, Porto, Portugal</t>
+        </is>
+      </c>
+      <c r="J16" s="12" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="K16" s="12" t="inlineStr">
+        <is>
+          <t>U13/U15/U17/U19 (B&amp;G)</t>
+        </is>
+      </c>
+      <c r="L16" s="12" t="inlineStr">
+        <is>
+          <t>ESF Junior Circuit Silver. Source: europeansquash.com/event/portuguese-junior-open-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>22 Jun 2026</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>27 Jun 2026</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>Eastern Slam 2026 ★</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="F17" s="11" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="G17" s="11" t="inlineStr"/>
+      <c r="H17" s="12" t="inlineStr">
+        <is>
           <t>India Squash / ASF</t>
         </is>
       </c>
-      <c r="I14" s="12" t="inlineStr">
+      <c r="I17" s="12" t="inlineStr">
         <is>
           <t>India (East)</t>
         </is>
       </c>
-      <c r="J14" s="12" t="inlineStr">
+      <c r="J17" s="12" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="K14" s="12" t="inlineStr">
+      <c r="K17" s="12" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L14" s="12" t="inlineStr">
+      <c r="L17" s="12" t="inlineStr">
         <is>
           <t>AJSS Silver. Source: asiansquash.org/eventpage/ajss-event</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>30 Jun 2026</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>5 Jul 2026</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>Tue</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>PBA 22nd Penang Junior Open 2026 ★</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F18" s="7" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr"/>
-      <c r="H15" s="8" t="inlineStr">
+      <c r="G18" s="7" t="inlineStr"/>
+      <c r="H18" s="8" t="inlineStr">
         <is>
           <t>Penang Squash / ASF</t>
         </is>
       </c>
-      <c r="I15" s="8" t="inlineStr">
+      <c r="I18" s="8" t="inlineStr">
         <is>
           <t>Penang, Malaysia</t>
         </is>
       </c>
-      <c r="J15" s="8" t="inlineStr">
+      <c r="J18" s="8" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="K15" s="8" t="inlineStr">
+      <c r="K18" s="8" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L15" s="8" t="inlineStr">
+      <c r="L18" s="8" t="inlineStr">
         <is>
           <t>AJSS Gold. Source: asiansquash.org/eventpage/ajss-event</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="25" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="25" t="inlineStr">
         <is>
           <t>2 Jul 2026</t>
         </is>
       </c>
-      <c r="B16" s="25" t="inlineStr">
+      <c r="B19" s="25" t="inlineStr">
         <is>
           <t>5 Jul 2026</t>
         </is>
       </c>
-      <c r="C16" s="25" t="inlineStr">
+      <c r="C19" s="25" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="D16" s="26" t="inlineStr">
+      <c r="D19" s="26" t="inlineStr">
         <is>
           <t>Dutch Junior Open 2026</t>
         </is>
       </c>
-      <c r="E16" s="26" t="inlineStr">
+      <c r="E19" s="26" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="F16" s="25" t="inlineStr">
+      <c r="F19" s="25" t="inlineStr">
         <is>
           <t>~ Estimated</t>
         </is>
       </c>
-      <c r="G16" s="25" t="inlineStr"/>
-      <c r="H16" s="26" t="inlineStr">
+      <c r="G19" s="25" t="inlineStr"/>
+      <c r="H19" s="26" t="inlineStr">
         <is>
           <t>ESF / Netherlands Squash</t>
         </is>
       </c>
-      <c r="I16" s="26" t="inlineStr">
+      <c r="I19" s="26" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="J16" s="26" t="inlineStr">
+      <c r="J19" s="26" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="K16" s="26" t="inlineStr">
+      <c r="K19" s="26" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L16" s="26" t="inlineStr">
+      <c r="L19" s="26" t="inlineStr">
         <is>
           <t>ESF Junior Circuit Gold. Finals confirmed 5 Jul 2026; start date estimated. Source: europeansquash.com</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>9 Jul 2026</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>12 Jul 2026</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="D20" s="10" t="inlineStr">
         <is>
           <t>European Junior Open 2026</t>
         </is>
       </c>
-      <c r="E17" s="10" t="inlineStr">
+      <c r="E20" s="10" t="inlineStr">
         <is>
           <t>Platinum</t>
         </is>
       </c>
-      <c r="F17" s="9" t="inlineStr">
+      <c r="F20" s="9" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G17" s="9" t="inlineStr"/>
-      <c r="H17" s="10" t="inlineStr">
+      <c r="G20" s="9" t="inlineStr"/>
+      <c r="H20" s="10" t="inlineStr">
         <is>
           <t>European Squash Federation (ESF)</t>
         </is>
       </c>
-      <c r="I17" s="10" t="inlineStr">
+      <c r="I20" s="10" t="inlineStr">
         <is>
           <t>Sportwerk Hamburg, Germany</t>
         </is>
       </c>
-      <c r="J17" s="10" t="inlineStr">
+      <c r="J20" s="10" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="K17" s="10" t="inlineStr">
+      <c r="K20" s="10" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L17" s="10" t="inlineStr">
+      <c r="L20" s="10" t="inlineStr">
         <is>
           <t>ESF Platinum. 215+ players. Second year at Hamburg. Source: europeansquash.com/event/european-junior-open-2026</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>15 Jul 2026</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>19 Jul 2026</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C21" s="11" t="inlineStr">
         <is>
           <t>Wed</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="D21" s="12" t="inlineStr">
         <is>
           <t>China Squash Junior Open 2026 ★</t>
         </is>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E21" s="12" t="inlineStr">
         <is>
           <t>Silver</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
+      <c r="F21" s="11" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G18" s="11" t="inlineStr"/>
-      <c r="H18" s="12" t="inlineStr">
+      <c r="G21" s="11" t="inlineStr"/>
+      <c r="H21" s="12" t="inlineStr">
         <is>
           <t>China Squash / ASF</t>
         </is>
       </c>
-      <c r="I18" s="12" t="inlineStr">
+      <c r="I21" s="12" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="J18" s="12" t="inlineStr">
+      <c r="J21" s="12" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="K18" s="12" t="inlineStr">
+      <c r="K21" s="12" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L18" s="12" t="inlineStr">
+      <c r="L21" s="12" t="inlineStr">
         <is>
           <t>AJSS Silver. Source: asiansquash.org/eventpage/ajss-event</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="27" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="27" t="inlineStr">
         <is>
           <t>20 Jul 2026</t>
         </is>
       </c>
-      <c r="B19" s="27" t="inlineStr">
+      <c r="B22" s="27" t="inlineStr">
         <is>
           <t>25 Jul 2026</t>
         </is>
       </c>
-      <c r="C19" s="27" t="inlineStr">
+      <c r="C22" s="27" t="inlineStr">
         <is>
           <t>Mon</t>
         </is>
       </c>
-      <c r="D19" s="28" t="inlineStr">
+      <c r="D22" s="28" t="inlineStr">
         <is>
           <t>WSF World Junior Championships 2026 — Individual</t>
         </is>
       </c>
-      <c r="E19" s="28" t="inlineStr">
+      <c r="E22" s="28" t="inlineStr">
         <is>
           <t>World Championship</t>
         </is>
       </c>
-      <c r="F19" s="27" t="inlineStr">
+      <c r="F22" s="27" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G19" s="27" t="inlineStr"/>
-      <c r="H19" s="28" t="inlineStr">
+      <c r="G22" s="27" t="inlineStr"/>
+      <c r="H22" s="28" t="inlineStr">
         <is>
           <t>World Squash Federation (WSF)</t>
         </is>
       </c>
-      <c r="I19" s="28" t="inlineStr">
+      <c r="I22" s="28" t="inlineStr">
         <is>
           <t>White Oaks Resort &amp; Spa, Niagara-on-the-Lake, Canada</t>
         </is>
       </c>
-      <c r="J19" s="28" t="inlineStr">
+      <c r="J22" s="28" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="K19" s="28" t="inlineStr">
+      <c r="K22" s="28" t="inlineStr">
         <is>
           <t>U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L19" s="28" t="inlineStr">
+      <c r="L22" s="28" t="inlineStr">
         <is>
           <t>185 players, 24+ nations. Champions: Mohamad Zakaria (EGY — first 3-time Men's World Junior Champion), Anahat Singh (IND). First in Canada since 1984. Source: worldsquash.sport</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="27" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="27" t="inlineStr">
         <is>
           <t>26 Jul 2026</t>
         </is>
       </c>
-      <c r="B20" s="27" t="inlineStr">
+      <c r="B23" s="27" t="inlineStr">
         <is>
           <t>31 Jul 2026</t>
         </is>
       </c>
-      <c r="C20" s="27" t="inlineStr">
+      <c r="C23" s="27" t="inlineStr">
         <is>
           <t>Sun</t>
         </is>
       </c>
-      <c r="D20" s="28" t="inlineStr">
+      <c r="D23" s="28" t="inlineStr">
         <is>
           <t>WSF World Junior Championships 2026 — Teams</t>
         </is>
       </c>
-      <c r="E20" s="28" t="inlineStr">
+      <c r="E23" s="28" t="inlineStr">
         <is>
           <t>World Championship</t>
         </is>
       </c>
-      <c r="F20" s="27" t="inlineStr">
+      <c r="F23" s="27" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G20" s="27" t="inlineStr"/>
-      <c r="H20" s="28" t="inlineStr">
+      <c r="G23" s="27" t="inlineStr"/>
+      <c r="H23" s="28" t="inlineStr">
         <is>
           <t>World Squash Federation (WSF)</t>
         </is>
       </c>
-      <c r="I20" s="28" t="inlineStr">
+      <c r="I23" s="28" t="inlineStr">
         <is>
           <t>White Oaks Resort &amp; Spa, Niagara-on-the-Lake, Canada</t>
         </is>
       </c>
-      <c r="J20" s="28" t="inlineStr">
+      <c r="J23" s="28" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="K20" s="28" t="inlineStr">
+      <c r="K23" s="28" t="inlineStr">
         <is>
           <t>U19 (B&amp;G — team format)</t>
         </is>
       </c>
-      <c r="L20" s="28" t="inlineStr">
+      <c r="L23" s="28" t="inlineStr">
         <is>
           <t>Boys: 8 pools of 3. Girls: 4 pools of 4. Nigeria debuted in women's teams. Source: worldsquash.sport</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="9" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>4 Aug 2026</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>9 Aug 2026</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>Tue</t>
         </is>
       </c>
-      <c r="D21" s="10" t="inlineStr">
+      <c r="D24" s="10" t="inlineStr">
         <is>
           <t>The JESSICA COMPANY Hong Kong Junior Squash Open 2026 ★</t>
         </is>
       </c>
-      <c r="E21" s="10" t="inlineStr">
+      <c r="E24" s="10" t="inlineStr">
         <is>
           <t>Platinum</t>
         </is>
       </c>
-      <c r="F21" s="9" t="inlineStr">
+      <c r="F24" s="9" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G21" s="9" t="inlineStr"/>
-      <c r="H21" s="10" t="inlineStr">
+      <c r="G24" s="9" t="inlineStr"/>
+      <c r="H24" s="10" t="inlineStr">
         <is>
           <t>Squash Association of Hong Kong, China (HKSA)</t>
         </is>
       </c>
-      <c r="I21" s="10" t="inlineStr">
+      <c r="I24" s="10" t="inlineStr">
         <is>
           <t>Cornwall St Squash Centre &amp; HK Squash Centre, Hong Kong</t>
         </is>
       </c>
-      <c r="J21" s="10" t="inlineStr">
+      <c r="J24" s="10" t="inlineStr">
         <is>
           <t>Hong Kong</t>
         </is>
       </c>
-      <c r="K21" s="10" t="inlineStr">
+      <c r="K24" s="10" t="inlineStr">
         <is>
           <t>U9/U11/U13/U15/U17/U19 (B&amp;G — 12 categories)</t>
         </is>
       </c>
-      <c r="L21" s="10" t="inlineStr">
+      <c r="L24" s="10" t="inlineStr">
         <is>
           <t>AJSS Platinum + WSF &amp; PSA Satellite Tour. Rounds/QF: 4-7 Aug (Cornwall St &amp; HKSC); SF/Final: 8-9 Aug (HKSC). PSA points: U17 &amp; U19. 850+ players from 16 countries. Sponsored by The Jessica Company; subvented by CSTB Arts &amp; Sport Dev Fund. Source: hksquash.org.hk + asiansquash.org</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>12 Aug 2026</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>15 Aug 2026</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>Wed</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="D25" s="8" t="inlineStr">
         <is>
           <t>19th Korea Junior Open 2026 ★</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="E25" s="8" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr">
+      <c r="F25" s="7" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G22" s="7" t="inlineStr"/>
-      <c r="H22" s="8" t="inlineStr">
+      <c r="G25" s="7" t="inlineStr"/>
+      <c r="H25" s="8" t="inlineStr">
         <is>
           <t>Korea Squash / ASF</t>
         </is>
       </c>
-      <c r="I22" s="8" t="inlineStr">
+      <c r="I25" s="8" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="J22" s="8" t="inlineStr">
+      <c r="J25" s="8" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="K22" s="8" t="inlineStr">
+      <c r="K25" s="8" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L22" s="8" t="inlineStr">
+      <c r="L25" s="8" t="inlineStr">
         <is>
           <t>AJSS Gold. Source: asiansquash.org/eventpage/ajss-event</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>17 Aug 2026</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>22 Aug 2026</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>Mon</t>
         </is>
       </c>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t>Southern Slam 2026 ★</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr">
+      <c r="E26" s="8" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="F23" s="7" t="inlineStr">
+      <c r="F26" s="7" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G23" s="7" t="inlineStr"/>
-      <c r="H23" s="8" t="inlineStr">
+      <c r="G26" s="7" t="inlineStr"/>
+      <c r="H26" s="8" t="inlineStr">
         <is>
           <t>India Squash / ASF</t>
         </is>
       </c>
-      <c r="I23" s="8" t="inlineStr">
+      <c r="I26" s="8" t="inlineStr">
         <is>
           <t>Chennai, India</t>
         </is>
       </c>
-      <c r="J23" s="8" t="inlineStr">
+      <c r="J26" s="8" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="K23" s="8" t="inlineStr">
+      <c r="K26" s="8" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L23" s="8" t="inlineStr">
+      <c r="L26" s="8" t="inlineStr">
         <is>
           <t>AJSS Gold. Entry deadline: 15 Jul 2026. Source: asiansquash.org/eventpage/ajss-event</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="11" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>19 Aug 2026</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>23 Aug 2026</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
+      <c r="C27" s="11" t="inlineStr">
         <is>
           <t>Wed</t>
         </is>
       </c>
-      <c r="D24" s="12" t="inlineStr">
+      <c r="D27" s="12" t="inlineStr">
         <is>
           <t>37th Japan Junior Open 2026 ★</t>
         </is>
       </c>
-      <c r="E24" s="12" t="inlineStr">
+      <c r="E27" s="12" t="inlineStr">
         <is>
           <t>Silver</t>
         </is>
       </c>
-      <c r="F24" s="11" t="inlineStr">
+      <c r="F27" s="11" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G24" s="11" t="inlineStr"/>
-      <c r="H24" s="12" t="inlineStr">
+      <c r="G27" s="11" t="inlineStr"/>
+      <c r="H27" s="12" t="inlineStr">
         <is>
           <t>Japan Squash / ASF</t>
         </is>
       </c>
-      <c r="I24" s="12" t="inlineStr">
+      <c r="I27" s="12" t="inlineStr">
         <is>
           <t>Yokohama &amp; Ebina, Japan</t>
         </is>
       </c>
-      <c r="J24" s="12" t="inlineStr">
+      <c r="J27" s="12" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="K24" s="12" t="inlineStr">
+      <c r="K27" s="12" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L24" s="12" t="inlineStr">
+      <c r="L27" s="12" t="inlineStr">
         <is>
           <t>AJSS Silver. Entry deadline: 25 Jun 2026 12:00 JST. Source: asiansquash.org/eventpage/ajss-event</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="11" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>25 Aug 2026</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>27 Aug 2026</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
+      <c r="C28" s="11" t="inlineStr">
         <is>
           <t>Tue</t>
         </is>
       </c>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="D28" s="12" t="inlineStr">
         <is>
           <t>Qatar Junior Open 2026 ★</t>
         </is>
       </c>
-      <c r="E25" s="12" t="inlineStr">
+      <c r="E28" s="12" t="inlineStr">
         <is>
           <t>Silver</t>
         </is>
       </c>
-      <c r="F25" s="11" t="inlineStr">
+      <c r="F28" s="11" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G25" s="11" t="inlineStr"/>
-      <c r="H25" s="12" t="inlineStr">
+      <c r="G28" s="11" t="inlineStr"/>
+      <c r="H28" s="12" t="inlineStr">
         <is>
           <t>Qatar Squash / ASF</t>
         </is>
       </c>
-      <c r="I25" s="12" t="inlineStr">
+      <c r="I28" s="12" t="inlineStr">
         <is>
           <t>Doha, Qatar</t>
         </is>
       </c>
-      <c r="J25" s="12" t="inlineStr">
+      <c r="J28" s="12" t="inlineStr">
         <is>
           <t>Qatar</t>
         </is>
       </c>
-      <c r="K25" s="12" t="inlineStr">
+      <c r="K28" s="12" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L25" s="12" t="inlineStr">
+      <c r="L28" s="12" t="inlineStr">
         <is>
           <t>AJSS Silver. Entry deadline: 6 Aug 2026. Source: asiansquash.org/eventpage/ajss-event</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="11" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
         <is>
           <t>25 Aug 2026</t>
         </is>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B29" s="11" t="inlineStr">
         <is>
           <t>29 Aug 2026</t>
         </is>
       </c>
-      <c r="C26" s="11" t="inlineStr">
+      <c r="C29" s="11" t="inlineStr">
         <is>
           <t>Tue</t>
         </is>
       </c>
-      <c r="D26" s="12" t="inlineStr">
+      <c r="D29" s="12" t="inlineStr">
         <is>
           <t>1st Chinese Taipei Junior Squash Open 2026 ★</t>
         </is>
       </c>
-      <c r="E26" s="12" t="inlineStr">
+      <c r="E29" s="12" t="inlineStr">
         <is>
           <t>Silver</t>
         </is>
       </c>
-      <c r="F26" s="11" t="inlineStr">
+      <c r="F29" s="11" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G26" s="11" t="inlineStr"/>
-      <c r="H26" s="12" t="inlineStr">
+      <c r="G29" s="11" t="inlineStr"/>
+      <c r="H29" s="12" t="inlineStr">
         <is>
           <t>Chinese Taipei Squash / ASF</t>
         </is>
       </c>
-      <c r="I26" s="12" t="inlineStr">
+      <c r="I29" s="12" t="inlineStr">
         <is>
           <t>Taipei, Chinese Taipei</t>
         </is>
       </c>
-      <c r="J26" s="12" t="inlineStr">
+      <c r="J29" s="12" t="inlineStr">
         <is>
           <t>Chinese Taipei</t>
         </is>
       </c>
-      <c r="K26" s="12" t="inlineStr">
+      <c r="K29" s="12" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L26" s="12" t="inlineStr">
+      <c r="L29" s="12" t="inlineStr">
         <is>
           <t>AJSS Silver — inaugural edition. Entry deadline: 5 Aug 2026. Source: asiansquash.org/eventpage/ajss-event</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>26 Aug 2026</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>30 Aug 2026</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>Wed</t>
         </is>
       </c>
-      <c r="D27" s="8" t="inlineStr">
+      <c r="D30" s="8" t="inlineStr">
         <is>
           <t>Macau Junior Squash Open 2026 ★</t>
         </is>
       </c>
-      <c r="E27" s="8" t="inlineStr">
+      <c r="E30" s="8" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr">
+      <c r="F30" s="7" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G27" s="7" t="inlineStr"/>
-      <c r="H27" s="8" t="inlineStr">
+      <c r="G30" s="7" t="inlineStr"/>
+      <c r="H30" s="8" t="inlineStr">
         <is>
           <t>Macau Squash / ASF</t>
         </is>
       </c>
-      <c r="I27" s="8" t="inlineStr">
+      <c r="I30" s="8" t="inlineStr">
         <is>
           <t>Macau, China</t>
         </is>
       </c>
-      <c r="J27" s="8" t="inlineStr">
+      <c r="J30" s="8" t="inlineStr">
         <is>
           <t>Macau</t>
         </is>
       </c>
-      <c r="K27" s="8" t="inlineStr">
+      <c r="K30" s="8" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L27" s="8" t="inlineStr">
+      <c r="L30" s="8" t="inlineStr">
         <is>
           <t>AJSS Gold. Entry deadline: 29 Jul 2026 12:00 Macau Time. Source: asiansquash.org/eventpage/ajss-event</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>19 Sep 2026</t>
-        </is>
-      </c>
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>24 Sep 2026</t>
-        </is>
-      </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>Sat</t>
-        </is>
-      </c>
-      <c r="D28" s="10" t="inlineStr">
-        <is>
-          <t>Indian Junior Open 2026 ★</t>
-        </is>
-      </c>
-      <c r="E28" s="10" t="inlineStr">
-        <is>
-          <t>Platinum</t>
-        </is>
-      </c>
-      <c r="F28" s="9" t="inlineStr">
-        <is>
-          <t>✓ Confirmed</t>
-        </is>
-      </c>
-      <c r="G28" s="9" t="inlineStr"/>
-      <c r="H28" s="10" t="inlineStr">
-        <is>
-          <t>Squash Rackets Federation of India / ASF</t>
-        </is>
-      </c>
-      <c r="I28" s="10" t="inlineStr">
-        <is>
-          <t>Kolkata, India</t>
-        </is>
-      </c>
-      <c r="J28" s="10" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="K28" s="10" t="inlineStr">
-        <is>
-          <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
-        </is>
-      </c>
-      <c r="L28" s="10" t="inlineStr">
-        <is>
-          <t>AJSS Platinum. Entry deadline: 12 Aug 2026. Source: asiansquash.org/eventpage/ajss-event</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>10 Oct 2026</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>12 Oct 2026</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>Sat</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>US West Coast JCT 2026</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>National/Regional</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>✓ Confirmed</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="6" t="inlineStr">
-        <is>
-          <t>US Squash</t>
-        </is>
-      </c>
-      <c r="I29" s="6" t="inlineStr">
-        <is>
-          <t>Redwood Shores &amp; Redwood City, CA</t>
-        </is>
-      </c>
-      <c r="J29" s="6" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="K29" s="6" t="inlineStr">
-        <is>
-          <t>All junior age groups</t>
-        </is>
-      </c>
-      <c r="L29" s="6" t="inlineStr">
-        <is>
-          <t>US Squash Junior Championship Tour. Source: ussquash.org</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="29" t="inlineStr">
-        <is>
-          <t>13 Oct 2026</t>
-        </is>
-      </c>
-      <c r="B30" s="29" t="inlineStr">
-        <is>
-          <t>18 Oct 2026</t>
-        </is>
-      </c>
-      <c r="C30" s="29" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="D30" s="30" t="inlineStr">
-        <is>
-          <t>Milo All Star Malaysia Squash Junior Open 2026 ★</t>
-        </is>
-      </c>
-      <c r="E30" s="30" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="F30" s="29" t="inlineStr">
-        <is>
-          <t>✓ Confirmed</t>
-        </is>
-      </c>
-      <c r="G30" s="29" t="inlineStr"/>
-      <c r="H30" s="30" t="inlineStr">
-        <is>
-          <t>Squash Rackets Association of Malaysia / ASF</t>
-        </is>
-      </c>
-      <c r="I30" s="30" t="inlineStr">
-        <is>
-          <t>Kuala Lumpur, Malaysia</t>
-        </is>
-      </c>
-      <c r="J30" s="30" t="inlineStr">
-        <is>
-          <t>Malaysia</t>
-        </is>
-      </c>
-      <c r="K30" s="30" t="inlineStr">
-        <is>
-          <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
-        </is>
-      </c>
-      <c r="L30" s="30" t="inlineStr">
-        <is>
-          <t>AJSS Diamond — highest AJSS tier. Entry deadline: 14 Sep 2026 5pm Malaysian Time. Source: asiansquash.org/eventpage/ajss-event</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>24 Oct 2026</t>
+          <t>4 Sep 2026</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>28 Oct 2026</t>
+          <t>6 Sep 2026</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Colombo Junior Squash Open 2026 ★</t>
+          <t>Welsh Junior Open 2026</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
@@ -21453,1497 +21453,1961 @@
       <c r="G31" s="11" t="inlineStr"/>
       <c r="H31" s="12" t="inlineStr">
         <is>
+          <t>ESF / Squash Wales</t>
+        </is>
+      </c>
+      <c r="I31" s="12" t="inlineStr">
+        <is>
+          <t>Sport Wales National Centre, Cardiff</t>
+        </is>
+      </c>
+      <c r="J31" s="12" t="inlineStr">
+        <is>
+          <t>Wales</t>
+        </is>
+      </c>
+      <c r="K31" s="12" t="inlineStr">
+        <is>
+          <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
+        </is>
+      </c>
+      <c r="L31" s="12" t="inlineStr">
+        <is>
+          <t>ESF Junior Circuit Silver. Entry deadline was 14 Aug 2026. Source: europeansquash.com / scottishsquash.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Slovak Junior Open 2026</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>Bronze</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr"/>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>ESF / Slovak Squash Federation</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>Bratislava, Slovakia</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>ESF Junior Circuit Bronze. Source: europeansquash.com/event/slovak-junior-open-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>19 Sep 2026</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>24 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>Indian Junior Open 2026 ★</t>
+        </is>
+      </c>
+      <c r="E33" s="10" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="G33" s="9" t="inlineStr"/>
+      <c r="H33" s="10" t="inlineStr">
+        <is>
+          <t>Squash Rackets Federation of India / ASF</t>
+        </is>
+      </c>
+      <c r="I33" s="10" t="inlineStr">
+        <is>
+          <t>Kolkata, India</t>
+        </is>
+      </c>
+      <c r="J33" s="10" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="K33" s="10" t="inlineStr">
+        <is>
+          <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
+        </is>
+      </c>
+      <c r="L33" s="10" t="inlineStr">
+        <is>
+          <t>AJSS Platinum. Entry deadline: 12 Aug 2026. Source: asiansquash.org/eventpage/ajss-event</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>US West Coast JCT 2026</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>National/Regional</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr"/>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>US Squash</t>
+        </is>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>Redwood Shores &amp; Redwood City, CA</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="K34" s="6" t="inlineStr">
+        <is>
+          <t>All junior age groups</t>
+        </is>
+      </c>
+      <c r="L34" s="6" t="inlineStr">
+        <is>
+          <t>US Squash Junior Championship Tour. Source: ussquash.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="29" t="inlineStr">
+        <is>
+          <t>13 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B35" s="29" t="inlineStr">
+        <is>
+          <t>18 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C35" s="29" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D35" s="30" t="inlineStr">
+        <is>
+          <t>Milo All Star Malaysia Squash Junior Open 2026 ★</t>
+        </is>
+      </c>
+      <c r="E35" s="30" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="F35" s="29" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="G35" s="29" t="inlineStr"/>
+      <c r="H35" s="30" t="inlineStr">
+        <is>
+          <t>Squash Rackets Association of Malaysia / ASF</t>
+        </is>
+      </c>
+      <c r="I35" s="30" t="inlineStr">
+        <is>
+          <t>Kuala Lumpur, Malaysia</t>
+        </is>
+      </c>
+      <c r="J35" s="30" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="K35" s="30" t="inlineStr">
+        <is>
+          <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
+        </is>
+      </c>
+      <c r="L35" s="30" t="inlineStr">
+        <is>
+          <t>AJSS Diamond — highest AJSS tier. Entry deadline: 14 Sep 2026 5pm Malaysian Time. Source: asiansquash.org/eventpage/ajss-event</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>22 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B36" s="25" t="inlineStr">
+        <is>
+          <t>25 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C36" s="25" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="D36" s="26" t="inlineStr">
+        <is>
+          <t>French Junior Open 2026</t>
+        </is>
+      </c>
+      <c r="E36" s="26" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="F36" s="25" t="inlineStr">
+        <is>
+          <t>~ Estimated</t>
+        </is>
+      </c>
+      <c r="G36" s="25" t="inlineStr"/>
+      <c r="H36" s="26" t="inlineStr">
+        <is>
+          <t>ESF / French Squash Federation</t>
+        </is>
+      </c>
+      <c r="I36" s="26" t="inlineStr">
+        <is>
+          <t>France (venue TBC)</t>
+        </is>
+      </c>
+      <c r="J36" s="26" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K36" s="26" t="inlineStr">
+        <is>
+          <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
+        </is>
+      </c>
+      <c r="L36" s="26" t="inlineStr">
+        <is>
+          <t>ESF Junior Circuit Gold. Venue not yet confirmed. Source: europeansquash.com/event/french-junior-open-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>24 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>28 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>Colombo Junior Squash Open 2026 ★</t>
+        </is>
+      </c>
+      <c r="E37" s="12" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="F37" s="11" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="G37" s="11" t="inlineStr"/>
+      <c r="H37" s="12" t="inlineStr">
+        <is>
           <t>Sri Lanka Squash / ASF</t>
         </is>
       </c>
-      <c r="I31" s="12" t="inlineStr">
+      <c r="I37" s="12" t="inlineStr">
         <is>
           <t>Ratmalana, Sri Lanka</t>
         </is>
       </c>
-      <c r="J31" s="12" t="inlineStr">
+      <c r="J37" s="12" t="inlineStr">
         <is>
           <t>Sri Lanka</t>
         </is>
       </c>
-      <c r="K31" s="12" t="inlineStr">
+      <c r="K37" s="12" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L31" s="12" t="inlineStr">
+      <c r="L37" s="12" t="inlineStr">
         <is>
           <t>AJSS Silver. Entry deadline: 23 Sep 2026 23:59 Sri Lanka Time. Source: asiansquash.org/eventpage/ajss-event</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>31 Oct 2026</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>15 Nov 2026</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>Sat</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t>Hong Kong Junior Squash Championships 2026</t>
         </is>
       </c>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="E38" s="6" t="inlineStr">
         <is>
           <t>National/Regional</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>25 Sep 2026</t>
         </is>
       </c>
-      <c r="H32" s="6" t="inlineStr">
+      <c r="H38" s="6" t="inlineStr">
         <is>
           <t>Squash Association of Hong Kong, China (HKSA)</t>
         </is>
       </c>
-      <c r="I32" s="6" t="inlineStr">
+      <c r="I38" s="6" t="inlineStr">
         <is>
           <t>Cornwall Street STTC &amp; Hong Kong Squash Centre, Hong Kong</t>
         </is>
       </c>
-      <c r="J32" s="6" t="inlineStr">
+      <c r="J38" s="6" t="inlineStr">
         <is>
           <t>Hong Kong</t>
         </is>
       </c>
-      <c r="K32" s="6" t="inlineStr">
+      <c r="K38" s="6" t="inlineStr">
         <is>
           <t>U9/U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L32" s="6" t="inlineStr">
+      <c r="L38" s="6" t="inlineStr">
         <is>
           <t>HK Junior Ranking 3-star event. Played across 3 weekends: 31 Oct &amp; 1 Nov (CSPSC); 7-8 Nov (CSPSC); SF/Final 14-15 Nov (HKSC). Entry deadline: 25 Sep 2026. Source: hksquash.org.hk/public/tournaments/overview/id/391.html</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>13 Nov 2026</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>15 Nov 2026</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>Fri</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D39" s="6" t="inlineStr">
         <is>
           <t>US Mid-Atlantic JCT 2026</t>
         </is>
       </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="E39" s="6" t="inlineStr">
         <is>
           <t>National/Regional</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr"/>
+      <c r="H39" s="6" t="inlineStr">
         <is>
           <t>US Squash</t>
         </is>
       </c>
-      <c r="I33" s="6" t="inlineStr">
+      <c r="I39" s="6" t="inlineStr">
         <is>
           <t>Washington, D.C.</t>
         </is>
       </c>
-      <c r="J33" s="6" t="inlineStr">
+      <c r="J39" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="K33" s="6" t="inlineStr">
+      <c r="K39" s="6" t="inlineStr">
         <is>
           <t>All junior age groups</t>
         </is>
       </c>
-      <c r="L33" s="6" t="inlineStr">
+      <c r="L39" s="6" t="inlineStr">
         <is>
           <t>US Squash Junior Championship Tour. Source: ussquash.org</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="9" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="25" t="inlineStr">
+        <is>
+          <t>28 Nov 2026</t>
+        </is>
+      </c>
+      <c r="B40" s="25" t="inlineStr">
+        <is>
+          <t>30 Nov 2026</t>
+        </is>
+      </c>
+      <c r="C40" s="25" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="D40" s="26" t="inlineStr">
+        <is>
+          <t>Malta Junior Open 2026</t>
+        </is>
+      </c>
+      <c r="E40" s="26" t="inlineStr">
+        <is>
+          <t>Bronze</t>
+        </is>
+      </c>
+      <c r="F40" s="25" t="inlineStr">
+        <is>
+          <t>~ Estimated</t>
+        </is>
+      </c>
+      <c r="G40" s="25" t="inlineStr"/>
+      <c r="H40" s="26" t="inlineStr">
+        <is>
+          <t>ESF / Malta Squash</t>
+        </is>
+      </c>
+      <c r="I40" s="26" t="inlineStr">
+        <is>
+          <t>National Squash Centre, Malta</t>
+        </is>
+      </c>
+      <c r="J40" s="26" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="K40" s="26" t="inlineStr">
+        <is>
+          <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
+        </is>
+      </c>
+      <c r="L40" s="26" t="inlineStr">
+        <is>
+          <t>ESF Junior Circuit Bronze. Entry deadline: 20 Nov 2026 (exact event dates estimated). Source: europeansquash.com/event/malta-junior-open-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
         <is>
           <t>1 Dec 2026</t>
         </is>
       </c>
-      <c r="B34" s="9" t="inlineStr">
+      <c r="B41" s="9" t="inlineStr">
         <is>
           <t>6 Dec 2026</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
+      <c r="C41" s="9" t="inlineStr">
         <is>
           <t>Tue</t>
         </is>
       </c>
-      <c r="D34" s="10" t="inlineStr">
+      <c r="D41" s="10" t="inlineStr">
         <is>
           <t>REDtone 18th KL Junior Open Squash Championships 2026 ★</t>
         </is>
       </c>
-      <c r="E34" s="10" t="inlineStr">
+      <c r="E41" s="10" t="inlineStr">
         <is>
           <t>Platinum</t>
         </is>
       </c>
-      <c r="F34" s="9" t="inlineStr">
+      <c r="F41" s="9" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G34" s="9" t="inlineStr"/>
-      <c r="H34" s="10" t="inlineStr">
+      <c r="G41" s="9" t="inlineStr"/>
+      <c r="H41" s="10" t="inlineStr">
         <is>
           <t>KL Squash / ASF</t>
         </is>
       </c>
-      <c r="I34" s="10" t="inlineStr">
+      <c r="I41" s="10" t="inlineStr">
         <is>
           <t>Kuala Lumpur, Malaysia</t>
         </is>
       </c>
-      <c r="J34" s="10" t="inlineStr">
+      <c r="J41" s="10" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="K34" s="10" t="inlineStr">
+      <c r="K41" s="10" t="inlineStr">
         <is>
           <t>U9/U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L34" s="10" t="inlineStr">
+      <c r="L41" s="10" t="inlineStr">
         <is>
           <t>AJSS Platinum. Entry deadline: 1 Oct 2026. Source: asiansquash.org/eventpage/ajss-event</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="9" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
         <is>
           <t>8 Dec 2026</t>
         </is>
       </c>
-      <c r="B35" s="9" t="inlineStr">
+      <c r="B42" s="9" t="inlineStr">
         <is>
           <t>13 Dec 2026</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr">
+      <c r="C42" s="9" t="inlineStr">
         <is>
           <t>Tue</t>
         </is>
       </c>
-      <c r="D35" s="10" t="inlineStr">
+      <c r="D42" s="10" t="inlineStr">
         <is>
           <t>ONCOCARE Singapore Junior Open 2026 ★</t>
         </is>
       </c>
-      <c r="E35" s="10" t="inlineStr">
+      <c r="E42" s="10" t="inlineStr">
         <is>
           <t>Platinum</t>
         </is>
       </c>
-      <c r="F35" s="9" t="inlineStr">
+      <c r="F42" s="9" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G35" s="9" t="inlineStr"/>
-      <c r="H35" s="10" t="inlineStr">
+      <c r="G42" s="9" t="inlineStr"/>
+      <c r="H42" s="10" t="inlineStr">
         <is>
           <t>Singapore Squash Rackets Association (SSRA) / ASF</t>
         </is>
       </c>
-      <c r="I35" s="10" t="inlineStr">
+      <c r="I42" s="10" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="J35" s="10" t="inlineStr">
+      <c r="J42" s="10" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="K35" s="10" t="inlineStr">
+      <c r="K42" s="10" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L35" s="10" t="inlineStr">
+      <c r="L42" s="10" t="inlineStr">
         <is>
           <t>AJSS Platinum. Entry deadline: 1 Nov 2026. Source: asiansquash.org/eventpage/ajss-event</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="9" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
         <is>
           <t>19 Dec 2026</t>
         </is>
       </c>
-      <c r="B36" s="9" t="inlineStr">
+      <c r="B43" s="9" t="inlineStr">
         <is>
           <t>23 Dec 2026</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr">
+      <c r="C43" s="9" t="inlineStr">
         <is>
           <t>Sat</t>
         </is>
       </c>
-      <c r="D36" s="10" t="inlineStr">
+      <c r="D43" s="10" t="inlineStr">
         <is>
           <t>US Junior Open 2026</t>
         </is>
       </c>
-      <c r="E36" s="10" t="inlineStr">
+      <c r="E43" s="10" t="inlineStr">
         <is>
           <t>Platinum</t>
         </is>
       </c>
-      <c r="F36" s="9" t="inlineStr">
+      <c r="F43" s="9" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G36" s="9" t="inlineStr"/>
-      <c r="H36" s="10" t="inlineStr">
+      <c r="G43" s="9" t="inlineStr"/>
+      <c r="H43" s="10" t="inlineStr">
         <is>
           <t>US Squash</t>
         </is>
       </c>
-      <c r="I36" s="10" t="inlineStr">
+      <c r="I43" s="10" t="inlineStr">
         <is>
           <t>Philadelphia, PA</t>
         </is>
       </c>
-      <c r="J36" s="10" t="inlineStr">
+      <c r="J43" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="K36" s="10" t="inlineStr">
+      <c r="K43" s="10" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L36" s="10" t="inlineStr">
+      <c r="L43" s="10" t="inlineStr">
         <is>
           <t>One of the largest US junior squash events. Source: ussquash.org</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="25" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="25" t="inlineStr">
         <is>
           <t>20 Dec 2026</t>
         </is>
       </c>
-      <c r="B37" s="25" t="inlineStr">
+      <c r="B44" s="25" t="inlineStr">
         <is>
           <t>26 Dec 2026</t>
         </is>
       </c>
-      <c r="C37" s="25" t="inlineStr">
+      <c r="C44" s="25" t="inlineStr">
         <is>
           <t>Sun</t>
         </is>
       </c>
-      <c r="D37" s="26" t="inlineStr">
+      <c r="D44" s="26" t="inlineStr">
         <is>
           <t>HKFC International Junior Squash Open 2026 (est.)</t>
         </is>
       </c>
-      <c r="E37" s="26" t="inlineStr">
+      <c r="E44" s="26" t="inlineStr">
         <is>
           <t>Platinum</t>
         </is>
       </c>
-      <c r="F37" s="25" t="inlineStr">
+      <c r="F44" s="25" t="inlineStr">
         <is>
           <t>~ Estimated</t>
         </is>
       </c>
-      <c r="G37" s="25" t="inlineStr"/>
-      <c r="H37" s="26" t="inlineStr">
+      <c r="G44" s="25" t="inlineStr"/>
+      <c r="H44" s="26" t="inlineStr">
         <is>
           <t>Squash Association of Hong Kong, China (HKSA)</t>
         </is>
       </c>
-      <c r="I37" s="26" t="inlineStr">
+      <c r="I44" s="26" t="inlineStr">
         <is>
           <t>Hong Kong Football Club &amp; HK Squash Centre, Hong Kong</t>
         </is>
       </c>
-      <c r="J37" s="26" t="inlineStr">
+      <c r="J44" s="26" t="inlineStr">
         <is>
           <t>Hong Kong</t>
         </is>
       </c>
-      <c r="K37" s="26" t="inlineStr">
+      <c r="K44" s="26" t="inlineStr">
         <is>
           <t>U9/U11/U13/U15/U17/U19 (B&amp;G — 12 categories)</t>
         </is>
       </c>
-      <c r="L37" s="26" t="inlineStr">
+      <c r="L44" s="26" t="inlineStr">
         <is>
           <t>AJSS Platinum. NOT YET listed on ASF page — dates estimated from prior years (2025 edition: 19-24 Dec 2025). Check hksquash.org.hk for official announcement.</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="9" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="11" t="inlineStr">
+        <is>
+          <t>28 Dec 2026</t>
+        </is>
+      </c>
+      <c r="B45" s="11" t="inlineStr">
+        <is>
+          <t>30 Dec 2026</t>
+        </is>
+      </c>
+      <c r="C45" s="11" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="D45" s="12" t="inlineStr">
+        <is>
+          <t>Scottish Junior Open 2026</t>
+        </is>
+      </c>
+      <c r="E45" s="12" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="F45" s="11" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="G45" s="11" t="inlineStr"/>
+      <c r="H45" s="12" t="inlineStr">
+        <is>
+          <t>ESF / Scottish Squash</t>
+        </is>
+      </c>
+      <c r="I45" s="12" t="inlineStr">
+        <is>
+          <t>Oriam &amp; Edinburgh Sports Club, Edinburgh</t>
+        </is>
+      </c>
+      <c r="J45" s="12" t="inlineStr">
+        <is>
+          <t>Scotland</t>
+        </is>
+      </c>
+      <c r="K45" s="12" t="inlineStr">
+        <is>
+          <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
+        </is>
+      </c>
+      <c r="L45" s="12" t="inlineStr">
+        <is>
+          <t>ESF Junior Circuit Silver. Lead-in event to British Junior Open 2027. Source: scottishsquash.org / europeansquash.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
         <is>
           <t>2 Jan 2027</t>
         </is>
       </c>
-      <c r="B38" s="9" t="inlineStr">
+      <c r="B46" s="9" t="inlineStr">
         <is>
           <t>6 Jan 2027</t>
         </is>
       </c>
-      <c r="C38" s="9" t="inlineStr">
+      <c r="C46" s="9" t="inlineStr">
         <is>
           <t>Sat</t>
         </is>
       </c>
-      <c r="D38" s="10" t="inlineStr">
+      <c r="D46" s="10" t="inlineStr">
         <is>
           <t>British Junior Open 2027</t>
         </is>
       </c>
-      <c r="E38" s="10" t="inlineStr">
+      <c r="E46" s="10" t="inlineStr">
         <is>
           <t>Platinum</t>
         </is>
       </c>
-      <c r="F38" s="9" t="inlineStr">
+      <c r="F46" s="9" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G38" s="9" t="inlineStr"/>
-      <c r="H38" s="10" t="inlineStr">
+      <c r="G46" s="9" t="inlineStr"/>
+      <c r="H46" s="10" t="inlineStr">
         <is>
           <t>England Squash / BJO</t>
         </is>
       </c>
-      <c r="I38" s="10" t="inlineStr">
+      <c r="I46" s="10" t="inlineStr">
         <is>
           <t>Birmingham, England</t>
         </is>
       </c>
-      <c r="J38" s="10" t="inlineStr">
+      <c r="J46" s="10" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="K38" s="10" t="inlineStr">
+      <c r="K46" s="10" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L38" s="10" t="inlineStr">
+      <c r="L46" s="10" t="inlineStr">
         <is>
           <t>Officially confirmed 2-6 Jan 2027. 750+ players from 50+ countries. Source: britishjunioropen.com/save-the-dates-british-junior-open-2027</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="7" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
         <is>
           <t>14 Jan 2027</t>
         </is>
       </c>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="B47" s="7" t="inlineStr">
         <is>
           <t>17 Jan 2027</t>
         </is>
       </c>
-      <c r="C39" s="7" t="inlineStr">
+      <c r="C47" s="7" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="D39" s="8" t="inlineStr">
+      <c r="D47" s="8" t="inlineStr">
         <is>
           <t>Czech Junior Open 2027</t>
         </is>
       </c>
-      <c r="E39" s="8" t="inlineStr">
+      <c r="E47" s="8" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="F39" s="7" t="inlineStr">
+      <c r="F47" s="7" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G39" s="7" t="inlineStr"/>
-      <c r="H39" s="8" t="inlineStr">
+      <c r="G47" s="7" t="inlineStr"/>
+      <c r="H47" s="8" t="inlineStr">
         <is>
           <t>ESF / Czech Squash Federation</t>
         </is>
       </c>
-      <c r="I39" s="8" t="inlineStr">
+      <c r="I47" s="8" t="inlineStr">
         <is>
           <t>Prague, Czech Republic</t>
         </is>
       </c>
-      <c r="J39" s="8" t="inlineStr">
+      <c r="J47" s="8" t="inlineStr">
         <is>
           <t>Czech Republic</t>
         </is>
       </c>
-      <c r="K39" s="8" t="inlineStr">
+      <c r="K47" s="8" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L39" s="8" t="inlineStr">
+      <c r="L47" s="8" t="inlineStr">
         <is>
           <t>ESF Junior Circuit Gold. Source: europeansquash.com</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>16 Jan 2027</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>18 Jan 2027</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>Sat</t>
         </is>
       </c>
-      <c r="D40" s="6" t="inlineStr">
+      <c r="D48" s="6" t="inlineStr">
         <is>
           <t>US Connecticut JCT 2027</t>
         </is>
       </c>
-      <c r="E40" s="6" t="inlineStr">
+      <c r="E48" s="6" t="inlineStr">
         <is>
           <t>National/Regional</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="F48" s="5" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G40" s="5" t="inlineStr"/>
-      <c r="H40" s="6" t="inlineStr">
+      <c r="G48" s="5" t="inlineStr"/>
+      <c r="H48" s="6" t="inlineStr">
         <is>
           <t>US Squash</t>
         </is>
       </c>
-      <c r="I40" s="6" t="inlineStr">
+      <c r="I48" s="6" t="inlineStr">
         <is>
           <t>Stamford / Norwalk, CT</t>
         </is>
       </c>
-      <c r="J40" s="6" t="inlineStr">
+      <c r="J48" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="K40" s="6" t="inlineStr">
+      <c r="K48" s="6" t="inlineStr">
         <is>
           <t>All junior age groups</t>
         </is>
       </c>
-      <c r="L40" s="6" t="inlineStr">
+      <c r="L48" s="6" t="inlineStr">
         <is>
           <t>US Squash Junior Championship Tour. Source: ussquash.org</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>29 Jan 2027</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>31 Jan 2027</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>Fri</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D49" s="4" t="inlineStr">
         <is>
           <t>Slovenia Junior Open 2027</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
+      <c r="E49" s="4" t="inlineStr">
         <is>
           <t>Bronze</t>
         </is>
       </c>
-      <c r="F41" s="3" t="inlineStr">
+      <c r="F49" s="3" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G41" s="3" t="inlineStr"/>
-      <c r="H41" s="4" t="inlineStr">
+      <c r="G49" s="3" t="inlineStr"/>
+      <c r="H49" s="4" t="inlineStr">
         <is>
           <t>ESF / Squash Slovenia</t>
         </is>
       </c>
-      <c r="I41" s="4" t="inlineStr">
+      <c r="I49" s="4" t="inlineStr">
         <is>
           <t>Ljubljana, Slovenia</t>
         </is>
       </c>
-      <c r="J41" s="4" t="inlineStr">
+      <c r="J49" s="4" t="inlineStr">
         <is>
           <t>Slovenia</t>
         </is>
       </c>
-      <c r="K41" s="4" t="inlineStr">
+      <c r="K49" s="4" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L41" s="4" t="inlineStr">
+      <c r="L49" s="4" t="inlineStr">
         <is>
           <t>ESF Junior Circuit Bronze. Source: europeansquash.com</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="11" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="11" t="inlineStr">
         <is>
           <t>10 Feb 2027</t>
         </is>
       </c>
-      <c r="B42" s="11" t="inlineStr">
+      <c r="B50" s="11" t="inlineStr">
         <is>
           <t>14 Feb 2027</t>
         </is>
       </c>
-      <c r="C42" s="11" t="inlineStr">
+      <c r="C50" s="11" t="inlineStr">
         <is>
           <t>Wed</t>
         </is>
       </c>
-      <c r="D42" s="12" t="inlineStr">
+      <c r="D50" s="12" t="inlineStr">
         <is>
           <t>Sri Lanka Junior Squash Open 2027 ★</t>
         </is>
       </c>
-      <c r="E42" s="12" t="inlineStr">
+      <c r="E50" s="12" t="inlineStr">
         <is>
           <t>Silver</t>
         </is>
       </c>
-      <c r="F42" s="11" t="inlineStr">
+      <c r="F50" s="11" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G42" s="11" t="inlineStr"/>
-      <c r="H42" s="12" t="inlineStr">
+      <c r="G50" s="11" t="inlineStr"/>
+      <c r="H50" s="12" t="inlineStr">
         <is>
           <t>Sri Lanka Squash / ASF</t>
         </is>
       </c>
-      <c r="I42" s="12" t="inlineStr">
+      <c r="I50" s="12" t="inlineStr">
         <is>
           <t>Ratmalana, Sri Lanka</t>
         </is>
       </c>
-      <c r="J42" s="12" t="inlineStr">
+      <c r="J50" s="12" t="inlineStr">
         <is>
           <t>Sri Lanka</t>
         </is>
       </c>
-      <c r="K42" s="12" t="inlineStr">
+      <c r="K50" s="12" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L42" s="12" t="inlineStr">
+      <c r="L50" s="12" t="inlineStr">
         <is>
           <t>AJSS Silver. Entry deadline: 4 Jan 2027. Source: asiansquash.org/eventpage/ajss-event</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="11" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="11" t="inlineStr">
         <is>
           <t>11 Feb 2027</t>
         </is>
       </c>
-      <c r="B43" s="11" t="inlineStr">
+      <c r="B51" s="11" t="inlineStr">
         <is>
           <t>14 Feb 2027</t>
         </is>
       </c>
-      <c r="C43" s="11" t="inlineStr">
+      <c r="C51" s="11" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="D43" s="12" t="inlineStr">
+      <c r="D51" s="12" t="inlineStr">
         <is>
           <t>Swiss Junior Open 2027</t>
         </is>
       </c>
-      <c r="E43" s="12" t="inlineStr">
+      <c r="E51" s="12" t="inlineStr">
         <is>
           <t>Silver</t>
         </is>
       </c>
-      <c r="F43" s="11" t="inlineStr">
+      <c r="F51" s="11" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G43" s="11" t="inlineStr"/>
-      <c r="H43" s="12" t="inlineStr">
+      <c r="G51" s="11" t="inlineStr"/>
+      <c r="H51" s="12" t="inlineStr">
         <is>
           <t>ESF / Swiss Squash</t>
         </is>
       </c>
-      <c r="I43" s="12" t="inlineStr">
+      <c r="I51" s="12" t="inlineStr">
         <is>
           <t>Langnau am Albis, Switzerland</t>
         </is>
       </c>
-      <c r="J43" s="12" t="inlineStr">
+      <c r="J51" s="12" t="inlineStr">
         <is>
           <t>Switzerland</t>
         </is>
       </c>
-      <c r="K43" s="12" t="inlineStr">
+      <c r="K51" s="12" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L43" s="12" t="inlineStr">
+      <c r="L51" s="12" t="inlineStr">
         <is>
           <t>ESF Junior Circuit Silver. Source: europeansquash.com</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>13 Feb 2027</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>15 Feb 2027</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
         <is>
           <t>Sat</t>
         </is>
       </c>
-      <c r="D44" s="6" t="inlineStr">
+      <c r="D52" s="6" t="inlineStr">
         <is>
           <t>US Texas JCT 2027</t>
         </is>
       </c>
-      <c r="E44" s="6" t="inlineStr">
+      <c r="E52" s="6" t="inlineStr">
         <is>
           <t>National/Regional</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="F52" s="5" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G44" s="5" t="inlineStr"/>
-      <c r="H44" s="6" t="inlineStr">
+      <c r="G52" s="5" t="inlineStr"/>
+      <c r="H52" s="6" t="inlineStr">
         <is>
           <t>US Squash</t>
         </is>
       </c>
-      <c r="I44" s="6" t="inlineStr">
+      <c r="I52" s="6" t="inlineStr">
         <is>
           <t>Houston, TX</t>
         </is>
       </c>
-      <c r="J44" s="6" t="inlineStr">
+      <c r="J52" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="K44" s="6" t="inlineStr">
+      <c r="K52" s="6" t="inlineStr">
         <is>
           <t>All junior age groups</t>
         </is>
       </c>
-      <c r="L44" s="6" t="inlineStr">
+      <c r="L52" s="6" t="inlineStr">
         <is>
           <t>US Squash Junior Championship Tour. Source: ussquash.org</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="7" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
         <is>
           <t>18 Feb 2027</t>
         </is>
       </c>
-      <c r="B45" s="7" t="inlineStr">
+      <c r="B53" s="7" t="inlineStr">
         <is>
           <t>21 Feb 2027</t>
         </is>
       </c>
-      <c r="C45" s="7" t="inlineStr">
+      <c r="C53" s="7" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="D45" s="8" t="inlineStr">
+      <c r="D53" s="8" t="inlineStr">
         <is>
           <t>German Junior Open 2027</t>
         </is>
       </c>
-      <c r="E45" s="8" t="inlineStr">
+      <c r="E53" s="8" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="F45" s="7" t="inlineStr">
+      <c r="F53" s="7" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G45" s="7" t="inlineStr"/>
-      <c r="H45" s="8" t="inlineStr">
+      <c r="G53" s="7" t="inlineStr"/>
+      <c r="H53" s="8" t="inlineStr">
         <is>
           <t>ESF / German Squash Federation</t>
         </is>
       </c>
-      <c r="I45" s="8" t="inlineStr">
+      <c r="I53" s="8" t="inlineStr">
         <is>
           <t>Hamburg, Germany</t>
         </is>
       </c>
-      <c r="J45" s="8" t="inlineStr">
+      <c r="J53" s="8" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="K45" s="8" t="inlineStr">
+      <c r="K53" s="8" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L45" s="8" t="inlineStr">
+      <c r="L53" s="8" t="inlineStr">
         <is>
           <t>ESF Junior Circuit Gold. Source: europeansquash.com</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>19 Feb 2027</t>
         </is>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>21 Feb 2027</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
         <is>
           <t>Fri</t>
         </is>
       </c>
-      <c r="D46" s="6" t="inlineStr">
+      <c r="D54" s="6" t="inlineStr">
         <is>
           <t>US High School Championships 2027</t>
         </is>
       </c>
-      <c r="E46" s="6" t="inlineStr">
+      <c r="E54" s="6" t="inlineStr">
         <is>
           <t>National/Regional</t>
         </is>
       </c>
-      <c r="F46" s="5" t="inlineStr">
+      <c r="F54" s="5" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G46" s="5" t="inlineStr"/>
-      <c r="H46" s="6" t="inlineStr">
+      <c r="G54" s="5" t="inlineStr"/>
+      <c r="H54" s="6" t="inlineStr">
         <is>
           <t>US Squash</t>
         </is>
       </c>
-      <c r="I46" s="6" t="inlineStr">
+      <c r="I54" s="6" t="inlineStr">
         <is>
           <t>Philadelphia, PA</t>
         </is>
       </c>
-      <c r="J46" s="6" t="inlineStr">
+      <c r="J54" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="K46" s="6" t="inlineStr">
+      <c r="K54" s="6" t="inlineStr">
         <is>
           <t>High School age groups</t>
         </is>
       </c>
-      <c r="L46" s="6" t="inlineStr">
+      <c r="L54" s="6" t="inlineStr">
         <is>
           <t>US national high school squash championships. Source: ussquash.org</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="23" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="23" t="inlineStr">
         <is>
           <t>23 Feb 2027</t>
         </is>
       </c>
-      <c r="B47" s="23" t="inlineStr">
+      <c r="B55" s="23" t="inlineStr">
         <is>
           <t>27 Feb 2027</t>
         </is>
       </c>
-      <c r="C47" s="23" t="inlineStr">
+      <c r="C55" s="23" t="inlineStr">
         <is>
           <t>Tue</t>
         </is>
       </c>
-      <c r="D47" s="24" t="inlineStr">
+      <c r="D55" s="24" t="inlineStr">
         <is>
           <t>23rd Asian Junior Team Championships 2027</t>
         </is>
       </c>
-      <c r="E47" s="24" t="inlineStr">
+      <c r="E55" s="24" t="inlineStr">
         <is>
           <t>Asian Championship</t>
         </is>
       </c>
-      <c r="F47" s="23" t="inlineStr">
+      <c r="F55" s="23" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G47" s="23" t="inlineStr"/>
-      <c r="H47" s="24" t="inlineStr">
+      <c r="G55" s="23" t="inlineStr"/>
+      <c r="H55" s="24" t="inlineStr">
         <is>
           <t>Asian Squash Federation (ASF)</t>
         </is>
       </c>
-      <c r="I47" s="24" t="inlineStr">
+      <c r="I55" s="24" t="inlineStr">
         <is>
           <t>Thailand (venue TBC)</t>
         </is>
       </c>
-      <c r="J47" s="24" t="inlineStr">
+      <c r="J55" s="24" t="inlineStr">
         <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="K47" s="24" t="inlineStr">
+      <c r="K55" s="24" t="inlineStr">
         <is>
           <t>U19 (B&amp;G — team format)</t>
         </is>
       </c>
-      <c r="L47" s="24" t="inlineStr">
+      <c r="L55" s="24" t="inlineStr">
         <is>
           <t>Confirmed on ASF 2026-27 calendar. Exact venue TBC. Source: asiansquash.org + thesquashsite.com</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="11" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="11" t="inlineStr">
         <is>
           <t>26 Feb 2027</t>
         </is>
       </c>
-      <c r="B48" s="11" t="inlineStr">
+      <c r="B56" s="11" t="inlineStr">
         <is>
           <t>28 Feb 2027</t>
         </is>
       </c>
-      <c r="C48" s="11" t="inlineStr">
+      <c r="C56" s="11" t="inlineStr">
         <is>
           <t>Fri</t>
         </is>
       </c>
-      <c r="D48" s="12" t="inlineStr">
+      <c r="D56" s="12" t="inlineStr">
         <is>
           <t>Austrian Junior Open 2027</t>
         </is>
       </c>
-      <c r="E48" s="12" t="inlineStr">
+      <c r="E56" s="12" t="inlineStr">
         <is>
           <t>Silver</t>
         </is>
       </c>
-      <c r="F48" s="11" t="inlineStr">
+      <c r="F56" s="11" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G48" s="11" t="inlineStr"/>
-      <c r="H48" s="12" t="inlineStr">
+      <c r="G56" s="11" t="inlineStr"/>
+      <c r="H56" s="12" t="inlineStr">
         <is>
           <t>ESF / Austrian Squash Federation</t>
         </is>
       </c>
-      <c r="I48" s="12" t="inlineStr">
+      <c r="I56" s="12" t="inlineStr">
         <is>
           <t>Vienna, Austria</t>
         </is>
       </c>
-      <c r="J48" s="12" t="inlineStr">
+      <c r="J56" s="12" t="inlineStr">
         <is>
           <t>Austria</t>
         </is>
       </c>
-      <c r="K48" s="12" t="inlineStr">
+      <c r="K56" s="12" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L48" s="12" t="inlineStr">
+      <c r="L56" s="12" t="inlineStr">
         <is>
           <t>ESF Junior Circuit Silver. Source: europeansquash.com</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>12 Mar 2027</t>
         </is>
       </c>
-      <c r="B49" s="5" t="inlineStr">
+      <c r="B57" s="5" t="inlineStr">
         <is>
           <t>14 Mar 2027</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
+      <c r="C57" s="5" t="inlineStr">
         <is>
           <t>Fri</t>
         </is>
       </c>
-      <c r="D49" s="6" t="inlineStr">
+      <c r="D57" s="6" t="inlineStr">
         <is>
           <t>US Junior Squash Championships 2027</t>
         </is>
       </c>
-      <c r="E49" s="6" t="inlineStr">
+      <c r="E57" s="6" t="inlineStr">
         <is>
           <t>National/Regional</t>
         </is>
       </c>
-      <c r="F49" s="5" t="inlineStr">
+      <c r="F57" s="5" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G49" s="5" t="inlineStr"/>
-      <c r="H49" s="6" t="inlineStr">
+      <c r="G57" s="5" t="inlineStr"/>
+      <c r="H57" s="6" t="inlineStr">
         <is>
           <t>US Squash</t>
         </is>
       </c>
-      <c r="I49" s="6" t="inlineStr">
+      <c r="I57" s="6" t="inlineStr">
         <is>
           <t>Philadelphia, PA</t>
         </is>
       </c>
-      <c r="J49" s="6" t="inlineStr">
+      <c r="J57" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="K49" s="6" t="inlineStr">
+      <c r="K57" s="6" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L49" s="6" t="inlineStr">
+      <c r="L57" s="6" t="inlineStr">
         <is>
           <t>US national junior championships. Source: ussquash.org</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="3" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
         <is>
           <t>12 Mar 2027</t>
         </is>
       </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>14 Mar 2027</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t>Fri</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr">
+      <c r="D58" s="4" t="inlineStr">
         <is>
           <t>Croatian Junior Open 2027</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
+      <c r="E58" s="4" t="inlineStr">
         <is>
           <t>Bronze</t>
         </is>
       </c>
-      <c r="F50" s="3" t="inlineStr">
+      <c r="F58" s="3" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G50" s="3" t="inlineStr"/>
-      <c r="H50" s="4" t="inlineStr">
+      <c r="G58" s="3" t="inlineStr"/>
+      <c r="H58" s="4" t="inlineStr">
         <is>
           <t>ESF / Croatian Squash Federation</t>
         </is>
       </c>
-      <c r="I50" s="4" t="inlineStr">
+      <c r="I58" s="4" t="inlineStr">
         <is>
           <t>Zagreb, Croatia</t>
         </is>
       </c>
-      <c r="J50" s="4" t="inlineStr">
+      <c r="J58" s="4" t="inlineStr">
         <is>
           <t>Croatia</t>
         </is>
       </c>
-      <c r="K50" s="4" t="inlineStr">
+      <c r="K58" s="4" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L50" s="4" t="inlineStr">
+      <c r="L58" s="4" t="inlineStr">
         <is>
           <t>ESF Junior Circuit Bronze. Source: europeansquash.com</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
         <is>
           <t>19 Mar 2027</t>
         </is>
       </c>
-      <c r="B51" s="5" t="inlineStr">
+      <c r="B59" s="5" t="inlineStr">
         <is>
           <t>21 Mar 2027</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="C59" s="5" t="inlineStr">
         <is>
           <t>Fri</t>
         </is>
       </c>
-      <c r="D51" s="6" t="inlineStr">
+      <c r="D59" s="6" t="inlineStr">
         <is>
           <t>US Junior Divisional Championships 2027</t>
         </is>
       </c>
-      <c r="E51" s="6" t="inlineStr">
+      <c r="E59" s="6" t="inlineStr">
         <is>
           <t>National/Regional</t>
         </is>
       </c>
-      <c r="F51" s="5" t="inlineStr">
+      <c r="F59" s="5" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G51" s="5" t="inlineStr"/>
-      <c r="H51" s="6" t="inlineStr">
+      <c r="G59" s="5" t="inlineStr"/>
+      <c r="H59" s="6" t="inlineStr">
         <is>
           <t>US Squash</t>
         </is>
       </c>
-      <c r="I51" s="6" t="inlineStr">
+      <c r="I59" s="6" t="inlineStr">
         <is>
           <t>USA (venue TBC)</t>
         </is>
       </c>
-      <c r="J51" s="6" t="inlineStr">
+      <c r="J59" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="K51" s="6" t="inlineStr">
+      <c r="K59" s="6" t="inlineStr">
         <is>
           <t>All junior age groups</t>
         </is>
       </c>
-      <c r="L51" s="6" t="inlineStr">
+      <c r="L59" s="6" t="inlineStr">
         <is>
           <t>US Squash regional divisional event. Source: ussquash.org</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="3" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>19 Mar 2027</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t>21 Mar 2027</t>
         </is>
       </c>
-      <c r="C52" s="3" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t>Fri</t>
         </is>
       </c>
-      <c r="D52" s="4" t="inlineStr">
+      <c r="D60" s="4" t="inlineStr">
         <is>
           <t>Norwegian Junior Open 2027</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
+      <c r="E60" s="4" t="inlineStr">
         <is>
           <t>Bronze</t>
         </is>
       </c>
-      <c r="F52" s="3" t="inlineStr">
+      <c r="F60" s="3" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G52" s="3" t="inlineStr"/>
-      <c r="H52" s="4" t="inlineStr">
+      <c r="G60" s="3" t="inlineStr"/>
+      <c r="H60" s="4" t="inlineStr">
         <is>
           <t>ESF / Squash Norway</t>
         </is>
       </c>
-      <c r="I52" s="4" t="inlineStr">
+      <c r="I60" s="4" t="inlineStr">
         <is>
           <t>Lysaker, Norway</t>
         </is>
       </c>
-      <c r="J52" s="4" t="inlineStr">
+      <c r="J60" s="4" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="K52" s="4" t="inlineStr">
+      <c r="K60" s="4" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L52" s="4" t="inlineStr">
+      <c r="L60" s="4" t="inlineStr">
         <is>
           <t>ESF Junior Circuit Bronze. Source: europeansquash.com</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="27" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="27" t="inlineStr">
         <is>
           <t>27 Mar 2027</t>
         </is>
       </c>
-      <c r="B53" s="27" t="inlineStr">
+      <c r="B61" s="27" t="inlineStr">
         <is>
           <t>4 Apr 2027</t>
         </is>
       </c>
-      <c r="C53" s="27" t="inlineStr">
+      <c r="C61" s="27" t="inlineStr">
         <is>
           <t>Sat</t>
         </is>
       </c>
-      <c r="D53" s="28" t="inlineStr">
+      <c r="D61" s="28" t="inlineStr">
         <is>
           <t>PSA World Championships 2026-27</t>
         </is>
       </c>
-      <c r="E53" s="28" t="inlineStr">
+      <c r="E61" s="28" t="inlineStr">
         <is>
           <t>World Championship</t>
         </is>
       </c>
-      <c r="F53" s="27" t="inlineStr">
+      <c r="F61" s="27" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G53" s="27" t="inlineStr"/>
-      <c r="H53" s="28" t="inlineStr">
+      <c r="G61" s="27" t="inlineStr"/>
+      <c r="H61" s="28" t="inlineStr">
         <is>
           <t>PSA World Tour / England Squash</t>
         </is>
       </c>
-      <c r="I53" s="28" t="inlineStr">
+      <c r="I61" s="28" t="inlineStr">
         <is>
           <t>London, England</t>
         </is>
       </c>
-      <c r="J53" s="28" t="inlineStr">
+      <c r="J61" s="28" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="K53" s="28" t="inlineStr">
+      <c r="K61" s="28" t="inlineStr">
         <is>
           <t>Open (professional)</t>
         </is>
       </c>
-      <c r="L53" s="28" t="inlineStr">
+      <c r="L61" s="28" t="inlineStr">
         <is>
           <t>Professional event — included for reference. Source: worldsquashchamps.com</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="27" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="27" t="inlineStr">
         <is>
           <t>7 Jun 2027</t>
         </is>
       </c>
-      <c r="B54" s="27" t="inlineStr">
+      <c r="B62" s="27" t="inlineStr">
         <is>
           <t>13 Jun 2027</t>
         </is>
       </c>
-      <c r="C54" s="27" t="inlineStr">
+      <c r="C62" s="27" t="inlineStr">
         <is>
           <t>Mon</t>
         </is>
       </c>
-      <c r="D54" s="28" t="inlineStr">
+      <c r="D62" s="28" t="inlineStr">
         <is>
           <t>WSF World Under-23 Championships 2027</t>
         </is>
       </c>
-      <c r="E54" s="28" t="inlineStr">
+      <c r="E62" s="28" t="inlineStr">
         <is>
           <t>World Championship</t>
         </is>
       </c>
-      <c r="F54" s="27" t="inlineStr">
+      <c r="F62" s="27" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G54" s="27" t="inlineStr"/>
-      <c r="H54" s="28" t="inlineStr">
+      <c r="G62" s="27" t="inlineStr"/>
+      <c r="H62" s="28" t="inlineStr">
         <is>
           <t>World Squash Federation (WSF)</t>
         </is>
       </c>
-      <c r="I54" s="28" t="inlineStr">
+      <c r="I62" s="28" t="inlineStr">
         <is>
           <t>Karachi, Pakistan</t>
         </is>
       </c>
-      <c r="J54" s="28" t="inlineStr">
+      <c r="J62" s="28" t="inlineStr">
         <is>
           <t>Pakistan</t>
         </is>
       </c>
-      <c r="K54" s="28" t="inlineStr">
+      <c r="K62" s="28" t="inlineStr">
         <is>
           <t>U23 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L54" s="28" t="inlineStr">
+      <c r="L62" s="28" t="inlineStr">
         <is>
           <t>WSF global event for under-23 players. Source: worldsquash.sport</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="31" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="31" t="inlineStr">
         <is>
           <t>COLOUR KEY — AJSS Levels: Diamond &gt; Platinum &gt; Gold &gt; Silver &gt; Bronze</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="28" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="28" t="inlineStr">
         <is>
           <t>World Championship</t>
         </is>
       </c>
-      <c r="B57" s="28" t="inlineStr">
+      <c r="B65" s="28" t="inlineStr">
         <is>
           <t>WSF / PSA global championship — pinnacle events</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="24" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="24" t="inlineStr">
         <is>
           <t>Asian Championship</t>
         </is>
       </c>
-      <c r="B58" s="24" t="inlineStr">
+      <c r="B66" s="24" t="inlineStr">
         <is>
           <t>ASF continental championships (Asian Junior Individual &amp; Team)</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="30" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="30" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="B59" s="30" t="inlineStr">
+      <c r="B67" s="30" t="inlineStr">
         <is>
           <t>AJSS Diamond — highest AJSS tier (e.g. Milo Malaysia)</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="10" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="10" t="inlineStr">
         <is>
           <t>Platinum</t>
         </is>
       </c>
-      <c r="B60" s="10" t="inlineStr">
+      <c r="B68" s="10" t="inlineStr">
         <is>
           <t>AJSS Platinum / ESF Platinum — highest open tier (HK Junior, BJO, Singapore JO, KL JO, Indian JO)</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="8" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="8" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="B61" s="8" t="inlineStr">
+      <c r="B69" s="8" t="inlineStr">
         <is>
           <t>AJSS Gold / ESF Gold — second tier (Korea, Japan, Penang, Lion City, Slams, Dutch JO, German JO)</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="12" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="12" t="inlineStr">
         <is>
           <t>Silver</t>
         </is>
       </c>
-      <c r="B62" s="12" t="inlineStr">
+      <c r="B70" s="12" t="inlineStr">
         <is>
           <t>AJSS Silver / ESF Silver — third tier (Sri Lanka, Australia, China, Qatar, Chinese Taipei, Swiss JO)</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="4" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
         <is>
           <t>Bronze</t>
         </is>
       </c>
-      <c r="B63" s="4" t="inlineStr">
+      <c r="B71" s="4" t="inlineStr">
         <is>
           <t>ESF Bronze — fourth tier European circuit (Slovenia, Croatia, Norway)</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="6" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
         <is>
           <t>National/Regional</t>
         </is>
       </c>
-      <c r="B64" s="6" t="inlineStr">
+      <c r="B72" s="6" t="inlineStr">
         <is>
           <t>National tour stops and domestic championships (US Squash JCT / High School / Divisional)</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="26" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="26" t="inlineStr">
         <is>
           <t>~ Estimated</t>
         </is>
       </c>
-      <c r="B65" s="26" t="inlineStr">
+      <c r="B73" s="26" t="inlineStr">
         <is>
           <t>AMBER = dates not yet officially confirmed — verify with the relevant federation before travel/planning</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:L54"/>
+  <autoFilter ref="A2:L62"/>
   <mergeCells count="11">
     <mergeCell ref="B65:L65"/>
-    <mergeCell ref="B58:L58"/>
-    <mergeCell ref="B62:L62"/>
-    <mergeCell ref="B64:L64"/>
+    <mergeCell ref="A64:L64"/>
+    <mergeCell ref="B73:L73"/>
+    <mergeCell ref="B70:L70"/>
+    <mergeCell ref="B68:L68"/>
     <mergeCell ref="A1:L1"/>
-    <mergeCell ref="B59:L59"/>
-    <mergeCell ref="A56:L56"/>
-    <mergeCell ref="B60:L60"/>
-    <mergeCell ref="B63:L63"/>
-    <mergeCell ref="B61:L61"/>
-    <mergeCell ref="B57:L57"/>
+    <mergeCell ref="B69:L69"/>
+    <mergeCell ref="B72:L72"/>
+    <mergeCell ref="B66:L66"/>
+    <mergeCell ref="B67:L67"/>
+    <mergeCell ref="B71:L71"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
